--- a/output/graficos_nacionales/plot_nacional_e_basneta_a_2022.xlsx
+++ b/output/graficos_nacionales/plot_nacional_e_basneta_a_2022.xlsx
@@ -88,12 +88,6 @@
     <t xml:space="preserve">Tortel</t>
   </si>
   <si>
-    <t xml:space="preserve">11201</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Aysén</t>
-  </si>
-  <si>
     <t xml:space="preserve">11202</t>
   </si>
   <si>
@@ -115,12 +109,6 @@
     <t xml:space="preserve">Laguna Blanca</t>
   </si>
   <si>
-    <t xml:space="preserve">11101</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Coyhaique</t>
-  </si>
-  <si>
     <t xml:space="preserve">12101</t>
   </si>
   <si>
@@ -397,6 +385,12 @@
     <t xml:space="preserve">Quinta de Tilcoco</t>
   </si>
   <si>
+    <t xml:space="preserve">6204</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Marchihue</t>
+  </si>
+  <si>
     <t xml:space="preserve">5705</t>
   </si>
   <si>
@@ -1330,6 +1324,12 @@
     <t xml:space="preserve">Tierra Amarilla</t>
   </si>
   <si>
+    <t xml:space="preserve">4105</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Paiguano</t>
+  </si>
+  <si>
     <t xml:space="preserve">2104</t>
   </si>
   <si>
@@ -2089,7 +2089,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-08 10:23</t>
+    <t xml:space="preserve">2026-09-09 20:12</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>
@@ -2697,7 +2697,7 @@
         <v>15</v>
       </c>
       <c r="I6" s="2" t="n">
-        <v>96.73</v>
+        <v>96.3</v>
       </c>
       <c r="J6" s="2" t="s">
         <v>16</v>
@@ -2708,16 +2708,16 @@
         <v>2022</v>
       </c>
       <c r="B7" s="2" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="E7" s="2" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="F7" s="2" t="s">
         <v>13</v>
@@ -2743,7 +2743,7 @@
         <v>12</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="D8" s="2" t="s">
         <v>28</v>
@@ -2761,7 +2761,7 @@
         <v>15</v>
       </c>
       <c r="I8" s="2" t="n">
-        <v>96.3</v>
+        <v>95.45</v>
       </c>
       <c r="J8" s="2" t="s">
         <v>16</v>
@@ -2775,7 +2775,7 @@
         <v>12</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="D9" s="2" t="s">
         <v>30</v>
@@ -2793,7 +2793,7 @@
         <v>15</v>
       </c>
       <c r="I9" s="2" t="n">
-        <v>95.45</v>
+        <v>94.9</v>
       </c>
       <c r="J9" s="2" t="s">
         <v>16</v>
@@ -2804,10 +2804,10 @@
         <v>2022</v>
       </c>
       <c r="B10" s="2" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="C10" s="2" t="s">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="D10" s="2" t="s">
         <v>32</v>
@@ -2825,7 +2825,7 @@
         <v>15</v>
       </c>
       <c r="I10" s="2" t="n">
-        <v>95.12</v>
+        <v>94.19</v>
       </c>
       <c r="J10" s="2" t="s">
         <v>16</v>
@@ -2839,7 +2839,7 @@
         <v>12</v>
       </c>
       <c r="C11" s="2" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="D11" s="2" t="s">
         <v>34</v>
@@ -2857,7 +2857,7 @@
         <v>15</v>
       </c>
       <c r="I11" s="2" t="n">
-        <v>94.9</v>
+        <v>93.89</v>
       </c>
       <c r="J11" s="2" t="s">
         <v>16</v>
@@ -2868,10 +2868,10 @@
         <v>2022</v>
       </c>
       <c r="B12" s="2" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="C12" s="2" t="s">
-        <v>27</v>
+        <v>10</v>
       </c>
       <c r="D12" s="2" t="s">
         <v>36</v>
@@ -2889,7 +2889,7 @@
         <v>15</v>
       </c>
       <c r="I12" s="2" t="n">
-        <v>94.19</v>
+        <v>93.55</v>
       </c>
       <c r="J12" s="2" t="s">
         <v>16</v>
@@ -2903,7 +2903,7 @@
         <v>12</v>
       </c>
       <c r="C13" s="2" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="D13" s="2" t="s">
         <v>38</v>
@@ -2921,7 +2921,7 @@
         <v>15</v>
       </c>
       <c r="I13" s="2" t="n">
-        <v>93.89</v>
+        <v>93.49</v>
       </c>
       <c r="J13" s="2" t="s">
         <v>16</v>
@@ -2932,10 +2932,10 @@
         <v>2022</v>
       </c>
       <c r="B14" s="2" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="C14" s="2" t="s">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="D14" s="2" t="s">
         <v>40</v>
@@ -2953,7 +2953,7 @@
         <v>15</v>
       </c>
       <c r="I14" s="2" t="n">
-        <v>93.55</v>
+        <v>87.5</v>
       </c>
       <c r="J14" s="2" t="s">
         <v>16</v>
@@ -2967,7 +2967,7 @@
         <v>12</v>
       </c>
       <c r="C15" s="2" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="D15" s="2" t="s">
         <v>42</v>
@@ -2985,7 +2985,7 @@
         <v>15</v>
       </c>
       <c r="I15" s="2" t="n">
-        <v>93.49</v>
+        <v>81.25</v>
       </c>
       <c r="J15" s="2" t="s">
         <v>16</v>
@@ -2996,28 +2996,28 @@
         <v>2022</v>
       </c>
       <c r="B16" s="2" t="n">
-        <v>12</v>
+        <v>7</v>
       </c>
       <c r="C16" s="2" t="s">
-        <v>27</v>
+        <v>44</v>
       </c>
       <c r="D16" s="2" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="E16" s="2" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="F16" s="2" t="s">
-        <v>13</v>
+        <v>47</v>
       </c>
       <c r="G16" s="2" t="s">
-        <v>14</v>
+        <v>48</v>
       </c>
       <c r="H16" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I16" s="2" t="n">
-        <v>87.5</v>
+        <v>98.39</v>
       </c>
       <c r="J16" s="2" t="s">
         <v>16</v>
@@ -3028,28 +3028,28 @@
         <v>2022</v>
       </c>
       <c r="B17" s="2" t="n">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="C17" s="2" t="s">
-        <v>27</v>
+        <v>49</v>
       </c>
       <c r="D17" s="2" t="s">
-        <v>46</v>
+        <v>50</v>
       </c>
       <c r="E17" s="2" t="s">
-        <v>47</v>
+        <v>51</v>
       </c>
       <c r="F17" s="2" t="s">
-        <v>13</v>
+        <v>47</v>
       </c>
       <c r="G17" s="2" t="s">
-        <v>14</v>
+        <v>48</v>
       </c>
       <c r="H17" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I17" s="2" t="n">
-        <v>81.25</v>
+        <v>98.32</v>
       </c>
       <c r="J17" s="2" t="s">
         <v>16</v>
@@ -3063,25 +3063,25 @@
         <v>7</v>
       </c>
       <c r="C18" s="2" t="s">
-        <v>48</v>
+        <v>44</v>
       </c>
       <c r="D18" s="2" t="s">
-        <v>49</v>
+        <v>52</v>
       </c>
       <c r="E18" s="2" t="s">
-        <v>50</v>
+        <v>53</v>
       </c>
       <c r="F18" s="2" t="s">
-        <v>51</v>
+        <v>47</v>
       </c>
       <c r="G18" s="2" t="s">
-        <v>52</v>
+        <v>48</v>
       </c>
       <c r="H18" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I18" s="2" t="n">
-        <v>98.39</v>
+        <v>98.29</v>
       </c>
       <c r="J18" s="2" t="s">
         <v>16</v>
@@ -3092,28 +3092,28 @@
         <v>2022</v>
       </c>
       <c r="B19" s="2" t="n">
-        <v>16</v>
+        <v>5</v>
       </c>
       <c r="C19" s="2" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="D19" s="2" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="E19" s="2" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="F19" s="2" t="s">
-        <v>51</v>
+        <v>47</v>
       </c>
       <c r="G19" s="2" t="s">
-        <v>52</v>
+        <v>48</v>
       </c>
       <c r="H19" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I19" s="2" t="n">
-        <v>98.32</v>
+        <v>97.72</v>
       </c>
       <c r="J19" s="2" t="s">
         <v>16</v>
@@ -3124,28 +3124,28 @@
         <v>2022</v>
       </c>
       <c r="B20" s="2" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C20" s="2" t="s">
-        <v>48</v>
+        <v>57</v>
       </c>
       <c r="D20" s="2" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="E20" s="2" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="F20" s="2" t="s">
-        <v>51</v>
+        <v>47</v>
       </c>
       <c r="G20" s="2" t="s">
-        <v>52</v>
+        <v>48</v>
       </c>
       <c r="H20" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I20" s="2" t="n">
-        <v>98.29</v>
+        <v>97.69</v>
       </c>
       <c r="J20" s="2" t="s">
         <v>16</v>
@@ -3156,28 +3156,28 @@
         <v>2022</v>
       </c>
       <c r="B21" s="2" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="C21" s="2" t="s">
-        <v>58</v>
+        <v>44</v>
       </c>
       <c r="D21" s="2" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="E21" s="2" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="F21" s="2" t="s">
-        <v>51</v>
+        <v>47</v>
       </c>
       <c r="G21" s="2" t="s">
-        <v>52</v>
+        <v>48</v>
       </c>
       <c r="H21" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I21" s="2" t="n">
-        <v>97.72</v>
+        <v>97.63</v>
       </c>
       <c r="J21" s="2" t="s">
         <v>16</v>
@@ -3188,10 +3188,10 @@
         <v>2022</v>
       </c>
       <c r="B22" s="2" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="C22" s="2" t="s">
-        <v>61</v>
+        <v>44</v>
       </c>
       <c r="D22" s="2" t="s">
         <v>62</v>
@@ -3200,16 +3200,16 @@
         <v>63</v>
       </c>
       <c r="F22" s="2" t="s">
-        <v>51</v>
+        <v>47</v>
       </c>
       <c r="G22" s="2" t="s">
-        <v>52</v>
+        <v>48</v>
       </c>
       <c r="H22" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I22" s="2" t="n">
-        <v>97.69</v>
+        <v>97.56</v>
       </c>
       <c r="J22" s="2" t="s">
         <v>16</v>
@@ -3220,10 +3220,10 @@
         <v>2022</v>
       </c>
       <c r="B23" s="2" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="C23" s="2" t="s">
-        <v>48</v>
+        <v>54</v>
       </c>
       <c r="D23" s="2" t="s">
         <v>64</v>
@@ -3232,16 +3232,16 @@
         <v>65</v>
       </c>
       <c r="F23" s="2" t="s">
-        <v>51</v>
+        <v>47</v>
       </c>
       <c r="G23" s="2" t="s">
-        <v>52</v>
+        <v>48</v>
       </c>
       <c r="H23" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I23" s="2" t="n">
-        <v>97.63</v>
+        <v>97.53</v>
       </c>
       <c r="J23" s="2" t="s">
         <v>16</v>
@@ -3252,10 +3252,10 @@
         <v>2022</v>
       </c>
       <c r="B24" s="2" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="C24" s="2" t="s">
-        <v>48</v>
+        <v>54</v>
       </c>
       <c r="D24" s="2" t="s">
         <v>66</v>
@@ -3264,16 +3264,16 @@
         <v>67</v>
       </c>
       <c r="F24" s="2" t="s">
-        <v>51</v>
+        <v>47</v>
       </c>
       <c r="G24" s="2" t="s">
-        <v>52</v>
+        <v>48</v>
       </c>
       <c r="H24" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I24" s="2" t="n">
-        <v>97.56</v>
+        <v>97.45</v>
       </c>
       <c r="J24" s="2" t="s">
         <v>16</v>
@@ -3284,10 +3284,10 @@
         <v>2022</v>
       </c>
       <c r="B25" s="2" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="C25" s="2" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="D25" s="2" t="s">
         <v>68</v>
@@ -3296,16 +3296,16 @@
         <v>69</v>
       </c>
       <c r="F25" s="2" t="s">
-        <v>51</v>
+        <v>47</v>
       </c>
       <c r="G25" s="2" t="s">
-        <v>52</v>
+        <v>48</v>
       </c>
       <c r="H25" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I25" s="2" t="n">
-        <v>97.53</v>
+        <v>97.41</v>
       </c>
       <c r="J25" s="2" t="s">
         <v>16</v>
@@ -3316,10 +3316,10 @@
         <v>2022</v>
       </c>
       <c r="B26" s="2" t="n">
-        <v>5</v>
+        <v>16</v>
       </c>
       <c r="C26" s="2" t="s">
-        <v>58</v>
+        <v>49</v>
       </c>
       <c r="D26" s="2" t="s">
         <v>70</v>
@@ -3328,16 +3328,16 @@
         <v>71</v>
       </c>
       <c r="F26" s="2" t="s">
-        <v>51</v>
+        <v>47</v>
       </c>
       <c r="G26" s="2" t="s">
-        <v>52</v>
+        <v>48</v>
       </c>
       <c r="H26" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I26" s="2" t="n">
-        <v>97.45</v>
+        <v>97.38</v>
       </c>
       <c r="J26" s="2" t="s">
         <v>16</v>
@@ -3348,10 +3348,10 @@
         <v>2022</v>
       </c>
       <c r="B27" s="2" t="n">
-        <v>6</v>
+        <v>16</v>
       </c>
       <c r="C27" s="2" t="s">
-        <v>61</v>
+        <v>49</v>
       </c>
       <c r="D27" s="2" t="s">
         <v>72</v>
@@ -3360,16 +3360,16 @@
         <v>73</v>
       </c>
       <c r="F27" s="2" t="s">
-        <v>51</v>
+        <v>47</v>
       </c>
       <c r="G27" s="2" t="s">
-        <v>52</v>
+        <v>48</v>
       </c>
       <c r="H27" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I27" s="2" t="n">
-        <v>97.41</v>
+        <v>97.36</v>
       </c>
       <c r="J27" s="2" t="s">
         <v>16</v>
@@ -3380,10 +3380,10 @@
         <v>2022</v>
       </c>
       <c r="B28" s="2" t="n">
-        <v>16</v>
+        <v>6</v>
       </c>
       <c r="C28" s="2" t="s">
-        <v>53</v>
+        <v>57</v>
       </c>
       <c r="D28" s="2" t="s">
         <v>74</v>
@@ -3392,16 +3392,16 @@
         <v>75</v>
       </c>
       <c r="F28" s="2" t="s">
-        <v>51</v>
+        <v>47</v>
       </c>
       <c r="G28" s="2" t="s">
-        <v>52</v>
+        <v>48</v>
       </c>
       <c r="H28" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I28" s="2" t="n">
-        <v>97.38</v>
+        <v>97.29</v>
       </c>
       <c r="J28" s="2" t="s">
         <v>16</v>
@@ -3412,10 +3412,10 @@
         <v>2022</v>
       </c>
       <c r="B29" s="2" t="n">
-        <v>16</v>
+        <v>7</v>
       </c>
       <c r="C29" s="2" t="s">
-        <v>53</v>
+        <v>44</v>
       </c>
       <c r="D29" s="2" t="s">
         <v>76</v>
@@ -3424,16 +3424,16 @@
         <v>77</v>
       </c>
       <c r="F29" s="2" t="s">
-        <v>51</v>
+        <v>47</v>
       </c>
       <c r="G29" s="2" t="s">
-        <v>52</v>
+        <v>48</v>
       </c>
       <c r="H29" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I29" s="2" t="n">
-        <v>97.36</v>
+        <v>97.25</v>
       </c>
       <c r="J29" s="2" t="s">
         <v>16</v>
@@ -3444,10 +3444,10 @@
         <v>2022</v>
       </c>
       <c r="B30" s="2" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="C30" s="2" t="s">
-        <v>61</v>
+        <v>44</v>
       </c>
       <c r="D30" s="2" t="s">
         <v>78</v>
@@ -3456,16 +3456,16 @@
         <v>79</v>
       </c>
       <c r="F30" s="2" t="s">
-        <v>51</v>
+        <v>47</v>
       </c>
       <c r="G30" s="2" t="s">
-        <v>52</v>
+        <v>48</v>
       </c>
       <c r="H30" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I30" s="2" t="n">
-        <v>97.29</v>
+        <v>97.24</v>
       </c>
       <c r="J30" s="2" t="s">
         <v>16</v>
@@ -3476,10 +3476,10 @@
         <v>2022</v>
       </c>
       <c r="B31" s="2" t="n">
-        <v>7</v>
+        <v>16</v>
       </c>
       <c r="C31" s="2" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="D31" s="2" t="s">
         <v>80</v>
@@ -3488,16 +3488,16 @@
         <v>81</v>
       </c>
       <c r="F31" s="2" t="s">
-        <v>51</v>
+        <v>47</v>
       </c>
       <c r="G31" s="2" t="s">
-        <v>52</v>
+        <v>48</v>
       </c>
       <c r="H31" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I31" s="2" t="n">
-        <v>97.25</v>
+        <v>97.21</v>
       </c>
       <c r="J31" s="2" t="s">
         <v>16</v>
@@ -3511,7 +3511,7 @@
         <v>7</v>
       </c>
       <c r="C32" s="2" t="s">
-        <v>48</v>
+        <v>44</v>
       </c>
       <c r="D32" s="2" t="s">
         <v>82</v>
@@ -3520,16 +3520,16 @@
         <v>83</v>
       </c>
       <c r="F32" s="2" t="s">
-        <v>51</v>
+        <v>47</v>
       </c>
       <c r="G32" s="2" t="s">
-        <v>52</v>
+        <v>48</v>
       </c>
       <c r="H32" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I32" s="2" t="n">
-        <v>97.24</v>
+        <v>97.14</v>
       </c>
       <c r="J32" s="2" t="s">
         <v>16</v>
@@ -3540,10 +3540,10 @@
         <v>2022</v>
       </c>
       <c r="B33" s="2" t="n">
-        <v>16</v>
+        <v>6</v>
       </c>
       <c r="C33" s="2" t="s">
-        <v>53</v>
+        <v>57</v>
       </c>
       <c r="D33" s="2" t="s">
         <v>84</v>
@@ -3552,16 +3552,16 @@
         <v>85</v>
       </c>
       <c r="F33" s="2" t="s">
-        <v>51</v>
+        <v>47</v>
       </c>
       <c r="G33" s="2" t="s">
-        <v>52</v>
+        <v>48</v>
       </c>
       <c r="H33" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I33" s="2" t="n">
-        <v>97.21</v>
+        <v>97.06</v>
       </c>
       <c r="J33" s="2" t="s">
         <v>16</v>
@@ -3572,10 +3572,10 @@
         <v>2022</v>
       </c>
       <c r="B34" s="2" t="n">
-        <v>7</v>
+        <v>16</v>
       </c>
       <c r="C34" s="2" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="D34" s="2" t="s">
         <v>86</v>
@@ -3584,16 +3584,16 @@
         <v>87</v>
       </c>
       <c r="F34" s="2" t="s">
-        <v>51</v>
+        <v>47</v>
       </c>
       <c r="G34" s="2" t="s">
-        <v>52</v>
+        <v>48</v>
       </c>
       <c r="H34" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I34" s="2" t="n">
-        <v>97.14</v>
+        <v>97.06</v>
       </c>
       <c r="J34" s="2" t="s">
         <v>16</v>
@@ -3607,7 +3607,7 @@
         <v>6</v>
       </c>
       <c r="C35" s="2" t="s">
-        <v>61</v>
+        <v>57</v>
       </c>
       <c r="D35" s="2" t="s">
         <v>88</v>
@@ -3616,16 +3616,16 @@
         <v>89</v>
       </c>
       <c r="F35" s="2" t="s">
-        <v>51</v>
+        <v>47</v>
       </c>
       <c r="G35" s="2" t="s">
-        <v>52</v>
+        <v>48</v>
       </c>
       <c r="H35" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I35" s="2" t="n">
-        <v>97.06</v>
+        <v>97.04</v>
       </c>
       <c r="J35" s="2" t="s">
         <v>16</v>
@@ -3636,10 +3636,10 @@
         <v>2022</v>
       </c>
       <c r="B36" s="2" t="n">
-        <v>16</v>
+        <v>7</v>
       </c>
       <c r="C36" s="2" t="s">
-        <v>53</v>
+        <v>44</v>
       </c>
       <c r="D36" s="2" t="s">
         <v>90</v>
@@ -3648,16 +3648,16 @@
         <v>91</v>
       </c>
       <c r="F36" s="2" t="s">
-        <v>51</v>
+        <v>47</v>
       </c>
       <c r="G36" s="2" t="s">
-        <v>52</v>
+        <v>48</v>
       </c>
       <c r="H36" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I36" s="2" t="n">
-        <v>97.06</v>
+        <v>97.04</v>
       </c>
       <c r="J36" s="2" t="s">
         <v>16</v>
@@ -3668,10 +3668,10 @@
         <v>2022</v>
       </c>
       <c r="B37" s="2" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="C37" s="2" t="s">
-        <v>61</v>
+        <v>44</v>
       </c>
       <c r="D37" s="2" t="s">
         <v>92</v>
@@ -3680,16 +3680,16 @@
         <v>93</v>
       </c>
       <c r="F37" s="2" t="s">
-        <v>51</v>
+        <v>47</v>
       </c>
       <c r="G37" s="2" t="s">
-        <v>52</v>
+        <v>48</v>
       </c>
       <c r="H37" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I37" s="2" t="n">
-        <v>97.04</v>
+        <v>97.03</v>
       </c>
       <c r="J37" s="2" t="s">
         <v>16</v>
@@ -3703,7 +3703,7 @@
         <v>7</v>
       </c>
       <c r="C38" s="2" t="s">
-        <v>48</v>
+        <v>44</v>
       </c>
       <c r="D38" s="2" t="s">
         <v>94</v>
@@ -3712,16 +3712,16 @@
         <v>95</v>
       </c>
       <c r="F38" s="2" t="s">
-        <v>51</v>
+        <v>47</v>
       </c>
       <c r="G38" s="2" t="s">
-        <v>52</v>
+        <v>48</v>
       </c>
       <c r="H38" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I38" s="2" t="n">
-        <v>97.04</v>
+        <v>97</v>
       </c>
       <c r="J38" s="2" t="s">
         <v>16</v>
@@ -3732,10 +3732,10 @@
         <v>2022</v>
       </c>
       <c r="B39" s="2" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="C39" s="2" t="s">
-        <v>48</v>
+        <v>54</v>
       </c>
       <c r="D39" s="2" t="s">
         <v>96</v>
@@ -3744,16 +3744,16 @@
         <v>97</v>
       </c>
       <c r="F39" s="2" t="s">
-        <v>51</v>
+        <v>47</v>
       </c>
       <c r="G39" s="2" t="s">
-        <v>52</v>
+        <v>48</v>
       </c>
       <c r="H39" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I39" s="2" t="n">
-        <v>97.03</v>
+        <v>96.94</v>
       </c>
       <c r="J39" s="2" t="s">
         <v>16</v>
@@ -3767,7 +3767,7 @@
         <v>7</v>
       </c>
       <c r="C40" s="2" t="s">
-        <v>48</v>
+        <v>44</v>
       </c>
       <c r="D40" s="2" t="s">
         <v>98</v>
@@ -3776,16 +3776,16 @@
         <v>99</v>
       </c>
       <c r="F40" s="2" t="s">
-        <v>51</v>
+        <v>47</v>
       </c>
       <c r="G40" s="2" t="s">
-        <v>52</v>
+        <v>48</v>
       </c>
       <c r="H40" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I40" s="2" t="n">
-        <v>97</v>
+        <v>96.9</v>
       </c>
       <c r="J40" s="2" t="s">
         <v>16</v>
@@ -3796,10 +3796,10 @@
         <v>2022</v>
       </c>
       <c r="B41" s="2" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="C41" s="2" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="D41" s="2" t="s">
         <v>100</v>
@@ -3808,16 +3808,16 @@
         <v>101</v>
       </c>
       <c r="F41" s="2" t="s">
-        <v>51</v>
+        <v>47</v>
       </c>
       <c r="G41" s="2" t="s">
-        <v>52</v>
+        <v>48</v>
       </c>
       <c r="H41" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I41" s="2" t="n">
-        <v>96.94</v>
+        <v>96.89</v>
       </c>
       <c r="J41" s="2" t="s">
         <v>16</v>
@@ -3831,7 +3831,7 @@
         <v>7</v>
       </c>
       <c r="C42" s="2" t="s">
-        <v>48</v>
+        <v>44</v>
       </c>
       <c r="D42" s="2" t="s">
         <v>102</v>
@@ -3840,16 +3840,16 @@
         <v>103</v>
       </c>
       <c r="F42" s="2" t="s">
-        <v>51</v>
+        <v>47</v>
       </c>
       <c r="G42" s="2" t="s">
-        <v>52</v>
+        <v>48</v>
       </c>
       <c r="H42" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I42" s="2" t="n">
-        <v>96.9</v>
+        <v>96.88</v>
       </c>
       <c r="J42" s="2" t="s">
         <v>16</v>
@@ -3860,10 +3860,10 @@
         <v>2022</v>
       </c>
       <c r="B43" s="2" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="C43" s="2" t="s">
-        <v>61</v>
+        <v>44</v>
       </c>
       <c r="D43" s="2" t="s">
         <v>104</v>
@@ -3872,16 +3872,16 @@
         <v>105</v>
       </c>
       <c r="F43" s="2" t="s">
-        <v>51</v>
+        <v>47</v>
       </c>
       <c r="G43" s="2" t="s">
-        <v>52</v>
+        <v>48</v>
       </c>
       <c r="H43" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I43" s="2" t="n">
-        <v>96.89</v>
+        <v>96.88</v>
       </c>
       <c r="J43" s="2" t="s">
         <v>16</v>
@@ -3892,10 +3892,10 @@
         <v>2022</v>
       </c>
       <c r="B44" s="2" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C44" s="2" t="s">
-        <v>48</v>
+        <v>57</v>
       </c>
       <c r="D44" s="2" t="s">
         <v>106</v>
@@ -3904,16 +3904,16 @@
         <v>107</v>
       </c>
       <c r="F44" s="2" t="s">
-        <v>51</v>
+        <v>47</v>
       </c>
       <c r="G44" s="2" t="s">
-        <v>52</v>
+        <v>48</v>
       </c>
       <c r="H44" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I44" s="2" t="n">
-        <v>96.88</v>
+        <v>96.87</v>
       </c>
       <c r="J44" s="2" t="s">
         <v>16</v>
@@ -3924,10 +3924,10 @@
         <v>2022</v>
       </c>
       <c r="B45" s="2" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C45" s="2" t="s">
-        <v>48</v>
+        <v>57</v>
       </c>
       <c r="D45" s="2" t="s">
         <v>108</v>
@@ -3936,16 +3936,16 @@
         <v>109</v>
       </c>
       <c r="F45" s="2" t="s">
-        <v>51</v>
+        <v>47</v>
       </c>
       <c r="G45" s="2" t="s">
-        <v>52</v>
+        <v>48</v>
       </c>
       <c r="H45" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I45" s="2" t="n">
-        <v>96.88</v>
+        <v>96.84</v>
       </c>
       <c r="J45" s="2" t="s">
         <v>16</v>
@@ -3959,7 +3959,7 @@
         <v>6</v>
       </c>
       <c r="C46" s="2" t="s">
-        <v>61</v>
+        <v>57</v>
       </c>
       <c r="D46" s="2" t="s">
         <v>110</v>
@@ -3968,16 +3968,16 @@
         <v>111</v>
       </c>
       <c r="F46" s="2" t="s">
-        <v>51</v>
+        <v>47</v>
       </c>
       <c r="G46" s="2" t="s">
-        <v>52</v>
+        <v>48</v>
       </c>
       <c r="H46" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I46" s="2" t="n">
-        <v>96.87</v>
+        <v>96.8</v>
       </c>
       <c r="J46" s="2" t="s">
         <v>16</v>
@@ -3988,10 +3988,10 @@
         <v>2022</v>
       </c>
       <c r="B47" s="2" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="C47" s="2" t="s">
-        <v>61</v>
+        <v>44</v>
       </c>
       <c r="D47" s="2" t="s">
         <v>112</v>
@@ -4000,16 +4000,16 @@
         <v>113</v>
       </c>
       <c r="F47" s="2" t="s">
-        <v>51</v>
+        <v>47</v>
       </c>
       <c r="G47" s="2" t="s">
-        <v>52</v>
+        <v>48</v>
       </c>
       <c r="H47" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I47" s="2" t="n">
-        <v>96.84</v>
+        <v>96.79</v>
       </c>
       <c r="J47" s="2" t="s">
         <v>16</v>
@@ -4020,10 +4020,10 @@
         <v>2022</v>
       </c>
       <c r="B48" s="2" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="C48" s="2" t="s">
-        <v>61</v>
+        <v>44</v>
       </c>
       <c r="D48" s="2" t="s">
         <v>114</v>
@@ -4032,16 +4032,16 @@
         <v>115</v>
       </c>
       <c r="F48" s="2" t="s">
-        <v>51</v>
+        <v>47</v>
       </c>
       <c r="G48" s="2" t="s">
-        <v>52</v>
+        <v>48</v>
       </c>
       <c r="H48" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I48" s="2" t="n">
-        <v>96.8</v>
+        <v>96.77</v>
       </c>
       <c r="J48" s="2" t="s">
         <v>16</v>
@@ -4052,10 +4052,10 @@
         <v>2022</v>
       </c>
       <c r="B49" s="2" t="n">
-        <v>7</v>
+        <v>16</v>
       </c>
       <c r="C49" s="2" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="D49" s="2" t="s">
         <v>116</v>
@@ -4064,16 +4064,16 @@
         <v>117</v>
       </c>
       <c r="F49" s="2" t="s">
-        <v>51</v>
+        <v>47</v>
       </c>
       <c r="G49" s="2" t="s">
-        <v>52</v>
+        <v>48</v>
       </c>
       <c r="H49" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I49" s="2" t="n">
-        <v>96.79</v>
+        <v>96.71</v>
       </c>
       <c r="J49" s="2" t="s">
         <v>16</v>
@@ -4084,10 +4084,10 @@
         <v>2022</v>
       </c>
       <c r="B50" s="2" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C50" s="2" t="s">
-        <v>48</v>
+        <v>57</v>
       </c>
       <c r="D50" s="2" t="s">
         <v>118</v>
@@ -4096,16 +4096,16 @@
         <v>119</v>
       </c>
       <c r="F50" s="2" t="s">
-        <v>51</v>
+        <v>47</v>
       </c>
       <c r="G50" s="2" t="s">
-        <v>52</v>
+        <v>48</v>
       </c>
       <c r="H50" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I50" s="2" t="n">
-        <v>96.77</v>
+        <v>96.7</v>
       </c>
       <c r="J50" s="2" t="s">
         <v>16</v>
@@ -4116,10 +4116,10 @@
         <v>2022</v>
       </c>
       <c r="B51" s="2" t="n">
-        <v>16</v>
+        <v>6</v>
       </c>
       <c r="C51" s="2" t="s">
-        <v>53</v>
+        <v>57</v>
       </c>
       <c r="D51" s="2" t="s">
         <v>120</v>
@@ -4128,16 +4128,16 @@
         <v>121</v>
       </c>
       <c r="F51" s="2" t="s">
-        <v>51</v>
+        <v>47</v>
       </c>
       <c r="G51" s="2" t="s">
-        <v>52</v>
+        <v>48</v>
       </c>
       <c r="H51" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I51" s="2" t="n">
-        <v>96.71</v>
+        <v>96.69</v>
       </c>
       <c r="J51" s="2" t="s">
         <v>16</v>
@@ -4151,7 +4151,7 @@
         <v>6</v>
       </c>
       <c r="C52" s="2" t="s">
-        <v>61</v>
+        <v>57</v>
       </c>
       <c r="D52" s="2" t="s">
         <v>122</v>
@@ -4160,16 +4160,16 @@
         <v>123</v>
       </c>
       <c r="F52" s="2" t="s">
-        <v>51</v>
+        <v>47</v>
       </c>
       <c r="G52" s="2" t="s">
-        <v>52</v>
+        <v>48</v>
       </c>
       <c r="H52" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I52" s="2" t="n">
-        <v>96.7</v>
+        <v>96.67</v>
       </c>
       <c r="J52" s="2" t="s">
         <v>16</v>
@@ -4180,10 +4180,10 @@
         <v>2022</v>
       </c>
       <c r="B53" s="2" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C53" s="2" t="s">
-        <v>61</v>
+        <v>54</v>
       </c>
       <c r="D53" s="2" t="s">
         <v>124</v>
@@ -4192,16 +4192,16 @@
         <v>125</v>
       </c>
       <c r="F53" s="2" t="s">
-        <v>51</v>
+        <v>47</v>
       </c>
       <c r="G53" s="2" t="s">
-        <v>52</v>
+        <v>48</v>
       </c>
       <c r="H53" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I53" s="2" t="n">
-        <v>96.69</v>
+        <v>96.66</v>
       </c>
       <c r="J53" s="2" t="s">
         <v>16</v>
@@ -4212,10 +4212,10 @@
         <v>2022</v>
       </c>
       <c r="B54" s="2" t="n">
-        <v>5</v>
+        <v>16</v>
       </c>
       <c r="C54" s="2" t="s">
-        <v>58</v>
+        <v>49</v>
       </c>
       <c r="D54" s="2" t="s">
         <v>126</v>
@@ -4224,16 +4224,16 @@
         <v>127</v>
       </c>
       <c r="F54" s="2" t="s">
-        <v>51</v>
+        <v>47</v>
       </c>
       <c r="G54" s="2" t="s">
-        <v>52</v>
+        <v>48</v>
       </c>
       <c r="H54" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I54" s="2" t="n">
-        <v>96.66</v>
+        <v>96.62</v>
       </c>
       <c r="J54" s="2" t="s">
         <v>16</v>
@@ -4244,10 +4244,10 @@
         <v>2022</v>
       </c>
       <c r="B55" s="2" t="n">
-        <v>16</v>
+        <v>7</v>
       </c>
       <c r="C55" s="2" t="s">
-        <v>53</v>
+        <v>44</v>
       </c>
       <c r="D55" s="2" t="s">
         <v>128</v>
@@ -4256,16 +4256,16 @@
         <v>129</v>
       </c>
       <c r="F55" s="2" t="s">
-        <v>51</v>
+        <v>47</v>
       </c>
       <c r="G55" s="2" t="s">
-        <v>52</v>
+        <v>48</v>
       </c>
       <c r="H55" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I55" s="2" t="n">
-        <v>96.62</v>
+        <v>96.61</v>
       </c>
       <c r="J55" s="2" t="s">
         <v>16</v>
@@ -4276,10 +4276,10 @@
         <v>2022</v>
       </c>
       <c r="B56" s="2" t="n">
-        <v>7</v>
+        <v>16</v>
       </c>
       <c r="C56" s="2" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="D56" s="2" t="s">
         <v>130</v>
@@ -4288,16 +4288,16 @@
         <v>131</v>
       </c>
       <c r="F56" s="2" t="s">
-        <v>51</v>
+        <v>47</v>
       </c>
       <c r="G56" s="2" t="s">
-        <v>52</v>
+        <v>48</v>
       </c>
       <c r="H56" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I56" s="2" t="n">
-        <v>96.61</v>
+        <v>96.57</v>
       </c>
       <c r="J56" s="2" t="s">
         <v>16</v>
@@ -4308,10 +4308,10 @@
         <v>2022</v>
       </c>
       <c r="B57" s="2" t="n">
-        <v>16</v>
+        <v>6</v>
       </c>
       <c r="C57" s="2" t="s">
-        <v>53</v>
+        <v>57</v>
       </c>
       <c r="D57" s="2" t="s">
         <v>132</v>
@@ -4320,16 +4320,16 @@
         <v>133</v>
       </c>
       <c r="F57" s="2" t="s">
-        <v>51</v>
+        <v>47</v>
       </c>
       <c r="G57" s="2" t="s">
-        <v>52</v>
+        <v>48</v>
       </c>
       <c r="H57" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I57" s="2" t="n">
-        <v>96.57</v>
+        <v>96.56</v>
       </c>
       <c r="J57" s="2" t="s">
         <v>16</v>
@@ -4340,10 +4340,10 @@
         <v>2022</v>
       </c>
       <c r="B58" s="2" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="C58" s="2" t="s">
-        <v>61</v>
+        <v>44</v>
       </c>
       <c r="D58" s="2" t="s">
         <v>134</v>
@@ -4352,16 +4352,16 @@
         <v>135</v>
       </c>
       <c r="F58" s="2" t="s">
-        <v>51</v>
+        <v>47</v>
       </c>
       <c r="G58" s="2" t="s">
-        <v>52</v>
+        <v>48</v>
       </c>
       <c r="H58" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I58" s="2" t="n">
-        <v>96.56</v>
+        <v>96.44</v>
       </c>
       <c r="J58" s="2" t="s">
         <v>16</v>
@@ -4372,10 +4372,10 @@
         <v>2022</v>
       </c>
       <c r="B59" s="2" t="n">
-        <v>7</v>
+        <v>16</v>
       </c>
       <c r="C59" s="2" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="D59" s="2" t="s">
         <v>136</v>
@@ -4384,16 +4384,16 @@
         <v>137</v>
       </c>
       <c r="F59" s="2" t="s">
-        <v>51</v>
+        <v>47</v>
       </c>
       <c r="G59" s="2" t="s">
-        <v>52</v>
+        <v>48</v>
       </c>
       <c r="H59" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I59" s="2" t="n">
-        <v>96.44</v>
+        <v>96.4</v>
       </c>
       <c r="J59" s="2" t="s">
         <v>16</v>
@@ -4407,7 +4407,7 @@
         <v>16</v>
       </c>
       <c r="C60" s="2" t="s">
-        <v>53</v>
+        <v>49</v>
       </c>
       <c r="D60" s="2" t="s">
         <v>138</v>
@@ -4416,16 +4416,16 @@
         <v>139</v>
       </c>
       <c r="F60" s="2" t="s">
-        <v>51</v>
+        <v>47</v>
       </c>
       <c r="G60" s="2" t="s">
-        <v>52</v>
+        <v>48</v>
       </c>
       <c r="H60" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I60" s="2" t="n">
-        <v>96.4</v>
+        <v>96.38</v>
       </c>
       <c r="J60" s="2" t="s">
         <v>16</v>
@@ -4436,10 +4436,10 @@
         <v>2022</v>
       </c>
       <c r="B61" s="2" t="n">
-        <v>16</v>
+        <v>7</v>
       </c>
       <c r="C61" s="2" t="s">
-        <v>53</v>
+        <v>44</v>
       </c>
       <c r="D61" s="2" t="s">
         <v>140</v>
@@ -4448,16 +4448,16 @@
         <v>141</v>
       </c>
       <c r="F61" s="2" t="s">
-        <v>51</v>
+        <v>47</v>
       </c>
       <c r="G61" s="2" t="s">
-        <v>52</v>
+        <v>48</v>
       </c>
       <c r="H61" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I61" s="2" t="n">
-        <v>96.38</v>
+        <v>96.37</v>
       </c>
       <c r="J61" s="2" t="s">
         <v>16</v>
@@ -4468,10 +4468,10 @@
         <v>2022</v>
       </c>
       <c r="B62" s="2" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="C62" s="2" t="s">
-        <v>48</v>
+        <v>54</v>
       </c>
       <c r="D62" s="2" t="s">
         <v>142</v>
@@ -4480,16 +4480,16 @@
         <v>143</v>
       </c>
       <c r="F62" s="2" t="s">
-        <v>51</v>
+        <v>47</v>
       </c>
       <c r="G62" s="2" t="s">
-        <v>52</v>
+        <v>48</v>
       </c>
       <c r="H62" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I62" s="2" t="n">
-        <v>96.37</v>
+        <v>96.36</v>
       </c>
       <c r="J62" s="2" t="s">
         <v>16</v>
@@ -4500,10 +4500,10 @@
         <v>2022</v>
       </c>
       <c r="B63" s="2" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="C63" s="2" t="s">
-        <v>58</v>
+        <v>44</v>
       </c>
       <c r="D63" s="2" t="s">
         <v>144</v>
@@ -4512,16 +4512,16 @@
         <v>145</v>
       </c>
       <c r="F63" s="2" t="s">
-        <v>51</v>
+        <v>47</v>
       </c>
       <c r="G63" s="2" t="s">
-        <v>52</v>
+        <v>48</v>
       </c>
       <c r="H63" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I63" s="2" t="n">
-        <v>96.36</v>
+        <v>96.31</v>
       </c>
       <c r="J63" s="2" t="s">
         <v>16</v>
@@ -4532,10 +4532,10 @@
         <v>2022</v>
       </c>
       <c r="B64" s="2" t="n">
-        <v>7</v>
+        <v>16</v>
       </c>
       <c r="C64" s="2" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="D64" s="2" t="s">
         <v>146</v>
@@ -4544,16 +4544,16 @@
         <v>147</v>
       </c>
       <c r="F64" s="2" t="s">
-        <v>51</v>
+        <v>47</v>
       </c>
       <c r="G64" s="2" t="s">
-        <v>52</v>
+        <v>48</v>
       </c>
       <c r="H64" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I64" s="2" t="n">
-        <v>96.31</v>
+        <v>96.3</v>
       </c>
       <c r="J64" s="2" t="s">
         <v>16</v>
@@ -4564,10 +4564,10 @@
         <v>2022</v>
       </c>
       <c r="B65" s="2" t="n">
-        <v>16</v>
+        <v>7</v>
       </c>
       <c r="C65" s="2" t="s">
-        <v>53</v>
+        <v>44</v>
       </c>
       <c r="D65" s="2" t="s">
         <v>148</v>
@@ -4576,16 +4576,16 @@
         <v>149</v>
       </c>
       <c r="F65" s="2" t="s">
-        <v>51</v>
+        <v>47</v>
       </c>
       <c r="G65" s="2" t="s">
-        <v>52</v>
+        <v>48</v>
       </c>
       <c r="H65" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I65" s="2" t="n">
-        <v>96.3</v>
+        <v>96.28</v>
       </c>
       <c r="J65" s="2" t="s">
         <v>16</v>
@@ -4596,10 +4596,10 @@
         <v>2022</v>
       </c>
       <c r="B66" s="2" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C66" s="2" t="s">
-        <v>48</v>
+        <v>57</v>
       </c>
       <c r="D66" s="2" t="s">
         <v>150</v>
@@ -4608,16 +4608,16 @@
         <v>151</v>
       </c>
       <c r="F66" s="2" t="s">
-        <v>51</v>
+        <v>47</v>
       </c>
       <c r="G66" s="2" t="s">
-        <v>52</v>
+        <v>48</v>
       </c>
       <c r="H66" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I66" s="2" t="n">
-        <v>96.28</v>
+        <v>96.27</v>
       </c>
       <c r="J66" s="2" t="s">
         <v>16</v>
@@ -4628,10 +4628,10 @@
         <v>2022</v>
       </c>
       <c r="B67" s="2" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C67" s="2" t="s">
-        <v>61</v>
+        <v>54</v>
       </c>
       <c r="D67" s="2" t="s">
         <v>152</v>
@@ -4640,16 +4640,16 @@
         <v>153</v>
       </c>
       <c r="F67" s="2" t="s">
-        <v>51</v>
+        <v>47</v>
       </c>
       <c r="G67" s="2" t="s">
-        <v>52</v>
+        <v>48</v>
       </c>
       <c r="H67" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I67" s="2" t="n">
-        <v>96.27</v>
+        <v>96.26</v>
       </c>
       <c r="J67" s="2" t="s">
         <v>16</v>
@@ -4660,10 +4660,10 @@
         <v>2022</v>
       </c>
       <c r="B68" s="2" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="C68" s="2" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="D68" s="2" t="s">
         <v>154</v>
@@ -4672,16 +4672,16 @@
         <v>155</v>
       </c>
       <c r="F68" s="2" t="s">
-        <v>51</v>
+        <v>47</v>
       </c>
       <c r="G68" s="2" t="s">
-        <v>52</v>
+        <v>48</v>
       </c>
       <c r="H68" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I68" s="2" t="n">
-        <v>96.26</v>
+        <v>96.25</v>
       </c>
       <c r="J68" s="2" t="s">
         <v>16</v>
@@ -4692,10 +4692,10 @@
         <v>2022</v>
       </c>
       <c r="B69" s="2" t="n">
-        <v>6</v>
+        <v>16</v>
       </c>
       <c r="C69" s="2" t="s">
-        <v>61</v>
+        <v>49</v>
       </c>
       <c r="D69" s="2" t="s">
         <v>156</v>
@@ -4704,10 +4704,10 @@
         <v>157</v>
       </c>
       <c r="F69" s="2" t="s">
-        <v>51</v>
+        <v>47</v>
       </c>
       <c r="G69" s="2" t="s">
-        <v>52</v>
+        <v>48</v>
       </c>
       <c r="H69" s="2" t="s">
         <v>15</v>
@@ -4724,10 +4724,10 @@
         <v>2022</v>
       </c>
       <c r="B70" s="2" t="n">
-        <v>16</v>
+        <v>6</v>
       </c>
       <c r="C70" s="2" t="s">
-        <v>53</v>
+        <v>57</v>
       </c>
       <c r="D70" s="2" t="s">
         <v>158</v>
@@ -4736,16 +4736,16 @@
         <v>159</v>
       </c>
       <c r="F70" s="2" t="s">
-        <v>51</v>
+        <v>47</v>
       </c>
       <c r="G70" s="2" t="s">
-        <v>52</v>
+        <v>48</v>
       </c>
       <c r="H70" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I70" s="2" t="n">
-        <v>96.25</v>
+        <v>96.23</v>
       </c>
       <c r="J70" s="2" t="s">
         <v>16</v>
@@ -4756,28 +4756,28 @@
         <v>2022</v>
       </c>
       <c r="B71" s="2" t="n">
-        <v>6</v>
+        <v>13</v>
       </c>
       <c r="C71" s="2" t="s">
-        <v>61</v>
+        <v>160</v>
       </c>
       <c r="D71" s="2" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="E71" s="2" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="F71" s="2" t="s">
-        <v>51</v>
+        <v>47</v>
       </c>
       <c r="G71" s="2" t="s">
-        <v>52</v>
+        <v>48</v>
       </c>
       <c r="H71" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I71" s="2" t="n">
-        <v>96.23</v>
+        <v>96.19</v>
       </c>
       <c r="J71" s="2" t="s">
         <v>16</v>
@@ -4788,10 +4788,10 @@
         <v>2022</v>
       </c>
       <c r="B72" s="2" t="n">
-        <v>13</v>
+        <v>6</v>
       </c>
       <c r="C72" s="2" t="s">
-        <v>162</v>
+        <v>57</v>
       </c>
       <c r="D72" s="2" t="s">
         <v>163</v>
@@ -4800,16 +4800,16 @@
         <v>164</v>
       </c>
       <c r="F72" s="2" t="s">
-        <v>51</v>
+        <v>47</v>
       </c>
       <c r="G72" s="2" t="s">
-        <v>52</v>
+        <v>48</v>
       </c>
       <c r="H72" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I72" s="2" t="n">
-        <v>96.19</v>
+        <v>96.18</v>
       </c>
       <c r="J72" s="2" t="s">
         <v>16</v>
@@ -4823,7 +4823,7 @@
         <v>6</v>
       </c>
       <c r="C73" s="2" t="s">
-        <v>61</v>
+        <v>57</v>
       </c>
       <c r="D73" s="2" t="s">
         <v>165</v>
@@ -4832,16 +4832,16 @@
         <v>166</v>
       </c>
       <c r="F73" s="2" t="s">
-        <v>51</v>
+        <v>47</v>
       </c>
       <c r="G73" s="2" t="s">
-        <v>52</v>
+        <v>48</v>
       </c>
       <c r="H73" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I73" s="2" t="n">
-        <v>96.18</v>
+        <v>96.16</v>
       </c>
       <c r="J73" s="2" t="s">
         <v>16</v>
@@ -4852,10 +4852,10 @@
         <v>2022</v>
       </c>
       <c r="B74" s="2" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="C74" s="2" t="s">
-        <v>61</v>
+        <v>44</v>
       </c>
       <c r="D74" s="2" t="s">
         <v>167</v>
@@ -4864,16 +4864,16 @@
         <v>168</v>
       </c>
       <c r="F74" s="2" t="s">
-        <v>51</v>
+        <v>47</v>
       </c>
       <c r="G74" s="2" t="s">
-        <v>52</v>
+        <v>48</v>
       </c>
       <c r="H74" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I74" s="2" t="n">
-        <v>96.16</v>
+        <v>96.14</v>
       </c>
       <c r="J74" s="2" t="s">
         <v>16</v>
@@ -4887,7 +4887,7 @@
         <v>7</v>
       </c>
       <c r="C75" s="2" t="s">
-        <v>48</v>
+        <v>44</v>
       </c>
       <c r="D75" s="2" t="s">
         <v>169</v>
@@ -4896,16 +4896,16 @@
         <v>170</v>
       </c>
       <c r="F75" s="2" t="s">
-        <v>51</v>
+        <v>47</v>
       </c>
       <c r="G75" s="2" t="s">
-        <v>52</v>
+        <v>48</v>
       </c>
       <c r="H75" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I75" s="2" t="n">
-        <v>96.14</v>
+        <v>96.09</v>
       </c>
       <c r="J75" s="2" t="s">
         <v>16</v>
@@ -4919,7 +4919,7 @@
         <v>7</v>
       </c>
       <c r="C76" s="2" t="s">
-        <v>48</v>
+        <v>44</v>
       </c>
       <c r="D76" s="2" t="s">
         <v>171</v>
@@ -4928,16 +4928,16 @@
         <v>172</v>
       </c>
       <c r="F76" s="2" t="s">
-        <v>51</v>
+        <v>47</v>
       </c>
       <c r="G76" s="2" t="s">
-        <v>52</v>
+        <v>48</v>
       </c>
       <c r="H76" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I76" s="2" t="n">
-        <v>96.09</v>
+        <v>96.08</v>
       </c>
       <c r="J76" s="2" t="s">
         <v>16</v>
@@ -4948,10 +4948,10 @@
         <v>2022</v>
       </c>
       <c r="B77" s="2" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="C77" s="2" t="s">
-        <v>48</v>
+        <v>54</v>
       </c>
       <c r="D77" s="2" t="s">
         <v>173</v>
@@ -4960,16 +4960,16 @@
         <v>174</v>
       </c>
       <c r="F77" s="2" t="s">
-        <v>51</v>
+        <v>47</v>
       </c>
       <c r="G77" s="2" t="s">
-        <v>52</v>
+        <v>48</v>
       </c>
       <c r="H77" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I77" s="2" t="n">
-        <v>96.08</v>
+        <v>96.07</v>
       </c>
       <c r="J77" s="2" t="s">
         <v>16</v>
@@ -4980,10 +4980,10 @@
         <v>2022</v>
       </c>
       <c r="B78" s="2" t="n">
-        <v>5</v>
+        <v>13</v>
       </c>
       <c r="C78" s="2" t="s">
-        <v>58</v>
+        <v>160</v>
       </c>
       <c r="D78" s="2" t="s">
         <v>175</v>
@@ -4992,10 +4992,10 @@
         <v>176</v>
       </c>
       <c r="F78" s="2" t="s">
-        <v>51</v>
+        <v>47</v>
       </c>
       <c r="G78" s="2" t="s">
-        <v>52</v>
+        <v>48</v>
       </c>
       <c r="H78" s="2" t="s">
         <v>15</v>
@@ -5012,10 +5012,10 @@
         <v>2022</v>
       </c>
       <c r="B79" s="2" t="n">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="C79" s="2" t="s">
-        <v>162</v>
+        <v>49</v>
       </c>
       <c r="D79" s="2" t="s">
         <v>177</v>
@@ -5024,10 +5024,10 @@
         <v>178</v>
       </c>
       <c r="F79" s="2" t="s">
-        <v>51</v>
+        <v>47</v>
       </c>
       <c r="G79" s="2" t="s">
-        <v>52</v>
+        <v>48</v>
       </c>
       <c r="H79" s="2" t="s">
         <v>15</v>
@@ -5044,10 +5044,10 @@
         <v>2022</v>
       </c>
       <c r="B80" s="2" t="n">
-        <v>16</v>
+        <v>7</v>
       </c>
       <c r="C80" s="2" t="s">
-        <v>53</v>
+        <v>44</v>
       </c>
       <c r="D80" s="2" t="s">
         <v>179</v>
@@ -5056,16 +5056,16 @@
         <v>180</v>
       </c>
       <c r="F80" s="2" t="s">
-        <v>51</v>
+        <v>47</v>
       </c>
       <c r="G80" s="2" t="s">
-        <v>52</v>
+        <v>48</v>
       </c>
       <c r="H80" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I80" s="2" t="n">
-        <v>96.07</v>
+        <v>96.04</v>
       </c>
       <c r="J80" s="2" t="s">
         <v>16</v>
@@ -5079,7 +5079,7 @@
         <v>7</v>
       </c>
       <c r="C81" s="2" t="s">
-        <v>48</v>
+        <v>44</v>
       </c>
       <c r="D81" s="2" t="s">
         <v>181</v>
@@ -5088,16 +5088,16 @@
         <v>182</v>
       </c>
       <c r="F81" s="2" t="s">
-        <v>51</v>
+        <v>47</v>
       </c>
       <c r="G81" s="2" t="s">
-        <v>52</v>
+        <v>48</v>
       </c>
       <c r="H81" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I81" s="2" t="n">
-        <v>96.04</v>
+        <v>96.02</v>
       </c>
       <c r="J81" s="2" t="s">
         <v>16</v>
@@ -5108,10 +5108,10 @@
         <v>2022</v>
       </c>
       <c r="B82" s="2" t="n">
-        <v>7</v>
+        <v>13</v>
       </c>
       <c r="C82" s="2" t="s">
-        <v>48</v>
+        <v>160</v>
       </c>
       <c r="D82" s="2" t="s">
         <v>183</v>
@@ -5120,16 +5120,16 @@
         <v>184</v>
       </c>
       <c r="F82" s="2" t="s">
-        <v>51</v>
+        <v>47</v>
       </c>
       <c r="G82" s="2" t="s">
-        <v>52</v>
+        <v>48</v>
       </c>
       <c r="H82" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I82" s="2" t="n">
-        <v>96.02</v>
+        <v>95.94</v>
       </c>
       <c r="J82" s="2" t="s">
         <v>16</v>
@@ -5140,28 +5140,28 @@
         <v>2022</v>
       </c>
       <c r="B83" s="2" t="n">
-        <v>13</v>
+        <v>7</v>
       </c>
       <c r="C83" s="2" t="s">
-        <v>162</v>
+        <v>44</v>
       </c>
       <c r="D83" s="2" t="s">
         <v>185</v>
       </c>
       <c r="E83" s="2" t="s">
-        <v>186</v>
+        <v>44</v>
       </c>
       <c r="F83" s="2" t="s">
-        <v>51</v>
+        <v>47</v>
       </c>
       <c r="G83" s="2" t="s">
-        <v>52</v>
+        <v>48</v>
       </c>
       <c r="H83" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I83" s="2" t="n">
-        <v>95.94</v>
+        <v>95.92</v>
       </c>
       <c r="J83" s="2" t="s">
         <v>16</v>
@@ -5172,28 +5172,28 @@
         <v>2022</v>
       </c>
       <c r="B84" s="2" t="n">
-        <v>7</v>
+        <v>16</v>
       </c>
       <c r="C84" s="2" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="D84" s="2" t="s">
+        <v>186</v>
+      </c>
+      <c r="E84" s="2" t="s">
         <v>187</v>
       </c>
-      <c r="E84" s="2" t="s">
-        <v>48</v>
-      </c>
       <c r="F84" s="2" t="s">
-        <v>51</v>
+        <v>47</v>
       </c>
       <c r="G84" s="2" t="s">
-        <v>52</v>
+        <v>48</v>
       </c>
       <c r="H84" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I84" s="2" t="n">
-        <v>95.92</v>
+        <v>95.9</v>
       </c>
       <c r="J84" s="2" t="s">
         <v>16</v>
@@ -5204,10 +5204,10 @@
         <v>2022</v>
       </c>
       <c r="B85" s="2" t="n">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="C85" s="2" t="s">
-        <v>53</v>
+        <v>160</v>
       </c>
       <c r="D85" s="2" t="s">
         <v>188</v>
@@ -5216,16 +5216,16 @@
         <v>189</v>
       </c>
       <c r="F85" s="2" t="s">
-        <v>51</v>
+        <v>47</v>
       </c>
       <c r="G85" s="2" t="s">
-        <v>52</v>
+        <v>48</v>
       </c>
       <c r="H85" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I85" s="2" t="n">
-        <v>95.9</v>
+        <v>95.89</v>
       </c>
       <c r="J85" s="2" t="s">
         <v>16</v>
@@ -5236,10 +5236,10 @@
         <v>2022</v>
       </c>
       <c r="B86" s="2" t="n">
-        <v>13</v>
+        <v>6</v>
       </c>
       <c r="C86" s="2" t="s">
-        <v>162</v>
+        <v>57</v>
       </c>
       <c r="D86" s="2" t="s">
         <v>190</v>
@@ -5248,16 +5248,16 @@
         <v>191</v>
       </c>
       <c r="F86" s="2" t="s">
-        <v>51</v>
+        <v>47</v>
       </c>
       <c r="G86" s="2" t="s">
-        <v>52</v>
+        <v>48</v>
       </c>
       <c r="H86" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I86" s="2" t="n">
-        <v>95.89</v>
+        <v>95.88</v>
       </c>
       <c r="J86" s="2" t="s">
         <v>16</v>
@@ -5271,7 +5271,7 @@
         <v>6</v>
       </c>
       <c r="C87" s="2" t="s">
-        <v>61</v>
+        <v>57</v>
       </c>
       <c r="D87" s="2" t="s">
         <v>192</v>
@@ -5280,16 +5280,16 @@
         <v>193</v>
       </c>
       <c r="F87" s="2" t="s">
-        <v>51</v>
+        <v>47</v>
       </c>
       <c r="G87" s="2" t="s">
-        <v>52</v>
+        <v>48</v>
       </c>
       <c r="H87" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I87" s="2" t="n">
-        <v>95.88</v>
+        <v>95.83</v>
       </c>
       <c r="J87" s="2" t="s">
         <v>16</v>
@@ -5300,10 +5300,10 @@
         <v>2022</v>
       </c>
       <c r="B88" s="2" t="n">
-        <v>6</v>
+        <v>16</v>
       </c>
       <c r="C88" s="2" t="s">
-        <v>61</v>
+        <v>49</v>
       </c>
       <c r="D88" s="2" t="s">
         <v>194</v>
@@ -5312,10 +5312,10 @@
         <v>195</v>
       </c>
       <c r="F88" s="2" t="s">
-        <v>51</v>
+        <v>47</v>
       </c>
       <c r="G88" s="2" t="s">
-        <v>52</v>
+        <v>48</v>
       </c>
       <c r="H88" s="2" t="s">
         <v>15</v>
@@ -5332,10 +5332,10 @@
         <v>2022</v>
       </c>
       <c r="B89" s="2" t="n">
-        <v>16</v>
+        <v>6</v>
       </c>
       <c r="C89" s="2" t="s">
-        <v>53</v>
+        <v>57</v>
       </c>
       <c r="D89" s="2" t="s">
         <v>196</v>
@@ -5344,16 +5344,16 @@
         <v>197</v>
       </c>
       <c r="F89" s="2" t="s">
-        <v>51</v>
+        <v>47</v>
       </c>
       <c r="G89" s="2" t="s">
-        <v>52</v>
+        <v>48</v>
       </c>
       <c r="H89" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I89" s="2" t="n">
-        <v>95.83</v>
+        <v>95.81</v>
       </c>
       <c r="J89" s="2" t="s">
         <v>16</v>
@@ -5364,10 +5364,10 @@
         <v>2022</v>
       </c>
       <c r="B90" s="2" t="n">
-        <v>6</v>
+        <v>13</v>
       </c>
       <c r="C90" s="2" t="s">
-        <v>61</v>
+        <v>160</v>
       </c>
       <c r="D90" s="2" t="s">
         <v>198</v>
@@ -5376,16 +5376,16 @@
         <v>199</v>
       </c>
       <c r="F90" s="2" t="s">
-        <v>51</v>
+        <v>47</v>
       </c>
       <c r="G90" s="2" t="s">
-        <v>52</v>
+        <v>48</v>
       </c>
       <c r="H90" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I90" s="2" t="n">
-        <v>95.81</v>
+        <v>95.75</v>
       </c>
       <c r="J90" s="2" t="s">
         <v>16</v>
@@ -5396,10 +5396,10 @@
         <v>2022</v>
       </c>
       <c r="B91" s="2" t="n">
-        <v>13</v>
+        <v>7</v>
       </c>
       <c r="C91" s="2" t="s">
-        <v>162</v>
+        <v>44</v>
       </c>
       <c r="D91" s="2" t="s">
         <v>200</v>
@@ -5408,16 +5408,16 @@
         <v>201</v>
       </c>
       <c r="F91" s="2" t="s">
-        <v>51</v>
+        <v>47</v>
       </c>
       <c r="G91" s="2" t="s">
-        <v>52</v>
+        <v>48</v>
       </c>
       <c r="H91" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I91" s="2" t="n">
-        <v>95.75</v>
+        <v>95.71</v>
       </c>
       <c r="J91" s="2" t="s">
         <v>16</v>
@@ -5428,10 +5428,10 @@
         <v>2022</v>
       </c>
       <c r="B92" s="2" t="n">
-        <v>7</v>
+        <v>16</v>
       </c>
       <c r="C92" s="2" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="D92" s="2" t="s">
         <v>202</v>
@@ -5440,16 +5440,16 @@
         <v>203</v>
       </c>
       <c r="F92" s="2" t="s">
-        <v>51</v>
+        <v>47</v>
       </c>
       <c r="G92" s="2" t="s">
-        <v>52</v>
+        <v>48</v>
       </c>
       <c r="H92" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I92" s="2" t="n">
-        <v>95.71</v>
+        <v>95.7</v>
       </c>
       <c r="J92" s="2" t="s">
         <v>16</v>
@@ -5463,7 +5463,7 @@
         <v>16</v>
       </c>
       <c r="C93" s="2" t="s">
-        <v>53</v>
+        <v>49</v>
       </c>
       <c r="D93" s="2" t="s">
         <v>204</v>
@@ -5472,16 +5472,16 @@
         <v>205</v>
       </c>
       <c r="F93" s="2" t="s">
-        <v>51</v>
+        <v>47</v>
       </c>
       <c r="G93" s="2" t="s">
-        <v>52</v>
+        <v>48</v>
       </c>
       <c r="H93" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I93" s="2" t="n">
-        <v>95.7</v>
+        <v>95.69</v>
       </c>
       <c r="J93" s="2" t="s">
         <v>16</v>
@@ -5492,10 +5492,10 @@
         <v>2022</v>
       </c>
       <c r="B94" s="2" t="n">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="C94" s="2" t="s">
-        <v>53</v>
+        <v>160</v>
       </c>
       <c r="D94" s="2" t="s">
         <v>206</v>
@@ -5504,16 +5504,16 @@
         <v>207</v>
       </c>
       <c r="F94" s="2" t="s">
-        <v>51</v>
+        <v>47</v>
       </c>
       <c r="G94" s="2" t="s">
-        <v>52</v>
+        <v>48</v>
       </c>
       <c r="H94" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I94" s="2" t="n">
-        <v>95.69</v>
+        <v>95.61</v>
       </c>
       <c r="J94" s="2" t="s">
         <v>16</v>
@@ -5527,7 +5527,7 @@
         <v>13</v>
       </c>
       <c r="C95" s="2" t="s">
-        <v>162</v>
+        <v>160</v>
       </c>
       <c r="D95" s="2" t="s">
         <v>208</v>
@@ -5536,16 +5536,16 @@
         <v>209</v>
       </c>
       <c r="F95" s="2" t="s">
-        <v>51</v>
+        <v>47</v>
       </c>
       <c r="G95" s="2" t="s">
-        <v>52</v>
+        <v>48</v>
       </c>
       <c r="H95" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I95" s="2" t="n">
-        <v>95.61</v>
+        <v>95.58</v>
       </c>
       <c r="J95" s="2" t="s">
         <v>16</v>
@@ -5556,10 +5556,10 @@
         <v>2022</v>
       </c>
       <c r="B96" s="2" t="n">
-        <v>13</v>
+        <v>7</v>
       </c>
       <c r="C96" s="2" t="s">
-        <v>162</v>
+        <v>44</v>
       </c>
       <c r="D96" s="2" t="s">
         <v>210</v>
@@ -5568,16 +5568,16 @@
         <v>211</v>
       </c>
       <c r="F96" s="2" t="s">
-        <v>51</v>
+        <v>47</v>
       </c>
       <c r="G96" s="2" t="s">
-        <v>52</v>
+        <v>48</v>
       </c>
       <c r="H96" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I96" s="2" t="n">
-        <v>95.58</v>
+        <v>95.53</v>
       </c>
       <c r="J96" s="2" t="s">
         <v>16</v>
@@ -5588,10 +5588,10 @@
         <v>2022</v>
       </c>
       <c r="B97" s="2" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="C97" s="2" t="s">
-        <v>48</v>
+        <v>54</v>
       </c>
       <c r="D97" s="2" t="s">
         <v>212</v>
@@ -5600,16 +5600,16 @@
         <v>213</v>
       </c>
       <c r="F97" s="2" t="s">
-        <v>51</v>
+        <v>47</v>
       </c>
       <c r="G97" s="2" t="s">
-        <v>52</v>
+        <v>48</v>
       </c>
       <c r="H97" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I97" s="2" t="n">
-        <v>95.53</v>
+        <v>95.5</v>
       </c>
       <c r="J97" s="2" t="s">
         <v>16</v>
@@ -5620,10 +5620,10 @@
         <v>2022</v>
       </c>
       <c r="B98" s="2" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="C98" s="2" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="D98" s="2" t="s">
         <v>214</v>
@@ -5632,16 +5632,16 @@
         <v>215</v>
       </c>
       <c r="F98" s="2" t="s">
-        <v>51</v>
+        <v>47</v>
       </c>
       <c r="G98" s="2" t="s">
-        <v>52</v>
+        <v>48</v>
       </c>
       <c r="H98" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I98" s="2" t="n">
-        <v>95.5</v>
+        <v>95.48</v>
       </c>
       <c r="J98" s="2" t="s">
         <v>16</v>
@@ -5652,10 +5652,10 @@
         <v>2022</v>
       </c>
       <c r="B99" s="2" t="n">
-        <v>6</v>
+        <v>13</v>
       </c>
       <c r="C99" s="2" t="s">
-        <v>61</v>
+        <v>160</v>
       </c>
       <c r="D99" s="2" t="s">
         <v>216</v>
@@ -5664,16 +5664,16 @@
         <v>217</v>
       </c>
       <c r="F99" s="2" t="s">
-        <v>51</v>
+        <v>47</v>
       </c>
       <c r="G99" s="2" t="s">
-        <v>52</v>
+        <v>48</v>
       </c>
       <c r="H99" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I99" s="2" t="n">
-        <v>95.48</v>
+        <v>95.44</v>
       </c>
       <c r="J99" s="2" t="s">
         <v>16</v>
@@ -5687,7 +5687,7 @@
         <v>13</v>
       </c>
       <c r="C100" s="2" t="s">
-        <v>162</v>
+        <v>160</v>
       </c>
       <c r="D100" s="2" t="s">
         <v>218</v>
@@ -5696,16 +5696,16 @@
         <v>219</v>
       </c>
       <c r="F100" s="2" t="s">
-        <v>51</v>
+        <v>47</v>
       </c>
       <c r="G100" s="2" t="s">
-        <v>52</v>
+        <v>48</v>
       </c>
       <c r="H100" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I100" s="2" t="n">
-        <v>95.44</v>
+        <v>95.28</v>
       </c>
       <c r="J100" s="2" t="s">
         <v>16</v>
@@ -5716,10 +5716,10 @@
         <v>2022</v>
       </c>
       <c r="B101" s="2" t="n">
-        <v>13</v>
+        <v>5</v>
       </c>
       <c r="C101" s="2" t="s">
-        <v>162</v>
+        <v>54</v>
       </c>
       <c r="D101" s="2" t="s">
         <v>220</v>
@@ -5728,16 +5728,16 @@
         <v>221</v>
       </c>
       <c r="F101" s="2" t="s">
-        <v>51</v>
+        <v>47</v>
       </c>
       <c r="G101" s="2" t="s">
-        <v>52</v>
+        <v>48</v>
       </c>
       <c r="H101" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I101" s="2" t="n">
-        <v>95.28</v>
+        <v>95.27</v>
       </c>
       <c r="J101" s="2" t="s">
         <v>16</v>
@@ -5751,7 +5751,7 @@
         <v>5</v>
       </c>
       <c r="C102" s="2" t="s">
-        <v>58</v>
+        <v>54</v>
       </c>
       <c r="D102" s="2" t="s">
         <v>222</v>
@@ -5760,16 +5760,16 @@
         <v>223</v>
       </c>
       <c r="F102" s="2" t="s">
-        <v>51</v>
+        <v>47</v>
       </c>
       <c r="G102" s="2" t="s">
-        <v>52</v>
+        <v>48</v>
       </c>
       <c r="H102" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I102" s="2" t="n">
-        <v>95.27</v>
+        <v>95.26</v>
       </c>
       <c r="J102" s="2" t="s">
         <v>16</v>
@@ -5783,7 +5783,7 @@
         <v>5</v>
       </c>
       <c r="C103" s="2" t="s">
-        <v>58</v>
+        <v>54</v>
       </c>
       <c r="D103" s="2" t="s">
         <v>224</v>
@@ -5792,16 +5792,16 @@
         <v>225</v>
       </c>
       <c r="F103" s="2" t="s">
-        <v>51</v>
+        <v>47</v>
       </c>
       <c r="G103" s="2" t="s">
-        <v>52</v>
+        <v>48</v>
       </c>
       <c r="H103" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I103" s="2" t="n">
-        <v>95.26</v>
+        <v>95.24</v>
       </c>
       <c r="J103" s="2" t="s">
         <v>16</v>
@@ -5812,10 +5812,10 @@
         <v>2022</v>
       </c>
       <c r="B104" s="2" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="C104" s="2" t="s">
-        <v>58</v>
+        <v>44</v>
       </c>
       <c r="D104" s="2" t="s">
         <v>226</v>
@@ -5824,10 +5824,10 @@
         <v>227</v>
       </c>
       <c r="F104" s="2" t="s">
-        <v>51</v>
+        <v>47</v>
       </c>
       <c r="G104" s="2" t="s">
-        <v>52</v>
+        <v>48</v>
       </c>
       <c r="H104" s="2" t="s">
         <v>15</v>
@@ -5844,10 +5844,10 @@
         <v>2022</v>
       </c>
       <c r="B105" s="2" t="n">
-        <v>7</v>
+        <v>13</v>
       </c>
       <c r="C105" s="2" t="s">
-        <v>48</v>
+        <v>160</v>
       </c>
       <c r="D105" s="2" t="s">
         <v>228</v>
@@ -5856,16 +5856,16 @@
         <v>229</v>
       </c>
       <c r="F105" s="2" t="s">
-        <v>51</v>
+        <v>47</v>
       </c>
       <c r="G105" s="2" t="s">
-        <v>52</v>
+        <v>48</v>
       </c>
       <c r="H105" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I105" s="2" t="n">
-        <v>95.24</v>
+        <v>95.22</v>
       </c>
       <c r="J105" s="2" t="s">
         <v>16</v>
@@ -5876,10 +5876,10 @@
         <v>2022</v>
       </c>
       <c r="B106" s="2" t="n">
-        <v>13</v>
+        <v>6</v>
       </c>
       <c r="C106" s="2" t="s">
-        <v>162</v>
+        <v>57</v>
       </c>
       <c r="D106" s="2" t="s">
         <v>230</v>
@@ -5888,16 +5888,16 @@
         <v>231</v>
       </c>
       <c r="F106" s="2" t="s">
-        <v>51</v>
+        <v>47</v>
       </c>
       <c r="G106" s="2" t="s">
-        <v>52</v>
+        <v>48</v>
       </c>
       <c r="H106" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I106" s="2" t="n">
-        <v>95.22</v>
+        <v>95.21</v>
       </c>
       <c r="J106" s="2" t="s">
         <v>16</v>
@@ -5911,7 +5911,7 @@
         <v>6</v>
       </c>
       <c r="C107" s="2" t="s">
-        <v>61</v>
+        <v>57</v>
       </c>
       <c r="D107" s="2" t="s">
         <v>232</v>
@@ -5920,10 +5920,10 @@
         <v>233</v>
       </c>
       <c r="F107" s="2" t="s">
-        <v>51</v>
+        <v>47</v>
       </c>
       <c r="G107" s="2" t="s">
-        <v>52</v>
+        <v>48</v>
       </c>
       <c r="H107" s="2" t="s">
         <v>15</v>
@@ -5943,7 +5943,7 @@
         <v>6</v>
       </c>
       <c r="C108" s="2" t="s">
-        <v>61</v>
+        <v>57</v>
       </c>
       <c r="D108" s="2" t="s">
         <v>234</v>
@@ -5952,16 +5952,16 @@
         <v>235</v>
       </c>
       <c r="F108" s="2" t="s">
-        <v>51</v>
+        <v>47</v>
       </c>
       <c r="G108" s="2" t="s">
-        <v>52</v>
+        <v>48</v>
       </c>
       <c r="H108" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I108" s="2" t="n">
-        <v>95.21</v>
+        <v>95.15</v>
       </c>
       <c r="J108" s="2" t="s">
         <v>16</v>
@@ -5972,10 +5972,10 @@
         <v>2022</v>
       </c>
       <c r="B109" s="2" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="C109" s="2" t="s">
-        <v>61</v>
+        <v>44</v>
       </c>
       <c r="D109" s="2" t="s">
         <v>236</v>
@@ -5984,10 +5984,10 @@
         <v>237</v>
       </c>
       <c r="F109" s="2" t="s">
-        <v>51</v>
+        <v>47</v>
       </c>
       <c r="G109" s="2" t="s">
-        <v>52</v>
+        <v>48</v>
       </c>
       <c r="H109" s="2" t="s">
         <v>15</v>
@@ -6004,10 +6004,10 @@
         <v>2022</v>
       </c>
       <c r="B110" s="2" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C110" s="2" t="s">
-        <v>48</v>
+        <v>57</v>
       </c>
       <c r="D110" s="2" t="s">
         <v>238</v>
@@ -6016,16 +6016,16 @@
         <v>239</v>
       </c>
       <c r="F110" s="2" t="s">
-        <v>51</v>
+        <v>47</v>
       </c>
       <c r="G110" s="2" t="s">
-        <v>52</v>
+        <v>48</v>
       </c>
       <c r="H110" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I110" s="2" t="n">
-        <v>95.15</v>
+        <v>95.12</v>
       </c>
       <c r="J110" s="2" t="s">
         <v>16</v>
@@ -6036,10 +6036,10 @@
         <v>2022</v>
       </c>
       <c r="B111" s="2" t="n">
-        <v>6</v>
+        <v>13</v>
       </c>
       <c r="C111" s="2" t="s">
-        <v>61</v>
+        <v>160</v>
       </c>
       <c r="D111" s="2" t="s">
         <v>240</v>
@@ -6048,16 +6048,16 @@
         <v>241</v>
       </c>
       <c r="F111" s="2" t="s">
-        <v>51</v>
+        <v>47</v>
       </c>
       <c r="G111" s="2" t="s">
-        <v>52</v>
+        <v>48</v>
       </c>
       <c r="H111" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I111" s="2" t="n">
-        <v>95.12</v>
+        <v>95.04</v>
       </c>
       <c r="J111" s="2" t="s">
         <v>16</v>
@@ -6071,7 +6071,7 @@
         <v>13</v>
       </c>
       <c r="C112" s="2" t="s">
-        <v>162</v>
+        <v>160</v>
       </c>
       <c r="D112" s="2" t="s">
         <v>242</v>
@@ -6080,16 +6080,16 @@
         <v>243</v>
       </c>
       <c r="F112" s="2" t="s">
-        <v>51</v>
+        <v>47</v>
       </c>
       <c r="G112" s="2" t="s">
-        <v>52</v>
+        <v>48</v>
       </c>
       <c r="H112" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I112" s="2" t="n">
-        <v>95.04</v>
+        <v>95.03</v>
       </c>
       <c r="J112" s="2" t="s">
         <v>16</v>
@@ -6100,10 +6100,10 @@
         <v>2022</v>
       </c>
       <c r="B113" s="2" t="n">
-        <v>13</v>
+        <v>5</v>
       </c>
       <c r="C113" s="2" t="s">
-        <v>162</v>
+        <v>54</v>
       </c>
       <c r="D113" s="2" t="s">
         <v>244</v>
@@ -6112,16 +6112,16 @@
         <v>245</v>
       </c>
       <c r="F113" s="2" t="s">
-        <v>51</v>
+        <v>47</v>
       </c>
       <c r="G113" s="2" t="s">
-        <v>52</v>
+        <v>48</v>
       </c>
       <c r="H113" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I113" s="2" t="n">
-        <v>95.03</v>
+        <v>94.95</v>
       </c>
       <c r="J113" s="2" t="s">
         <v>16</v>
@@ -6132,10 +6132,10 @@
         <v>2022</v>
       </c>
       <c r="B114" s="2" t="n">
-        <v>5</v>
+        <v>16</v>
       </c>
       <c r="C114" s="2" t="s">
-        <v>58</v>
+        <v>49</v>
       </c>
       <c r="D114" s="2" t="s">
         <v>246</v>
@@ -6144,16 +6144,16 @@
         <v>247</v>
       </c>
       <c r="F114" s="2" t="s">
-        <v>51</v>
+        <v>47</v>
       </c>
       <c r="G114" s="2" t="s">
-        <v>52</v>
+        <v>48</v>
       </c>
       <c r="H114" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I114" s="2" t="n">
-        <v>94.95</v>
+        <v>94.94</v>
       </c>
       <c r="J114" s="2" t="s">
         <v>16</v>
@@ -6164,10 +6164,10 @@
         <v>2022</v>
       </c>
       <c r="B115" s="2" t="n">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="C115" s="2" t="s">
-        <v>53</v>
+        <v>160</v>
       </c>
       <c r="D115" s="2" t="s">
         <v>248</v>
@@ -6176,16 +6176,16 @@
         <v>249</v>
       </c>
       <c r="F115" s="2" t="s">
-        <v>51</v>
+        <v>47</v>
       </c>
       <c r="G115" s="2" t="s">
-        <v>52</v>
+        <v>48</v>
       </c>
       <c r="H115" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I115" s="2" t="n">
-        <v>94.94</v>
+        <v>94.92</v>
       </c>
       <c r="J115" s="2" t="s">
         <v>16</v>
@@ -6196,10 +6196,10 @@
         <v>2022</v>
       </c>
       <c r="B116" s="2" t="n">
-        <v>13</v>
+        <v>5</v>
       </c>
       <c r="C116" s="2" t="s">
-        <v>162</v>
+        <v>54</v>
       </c>
       <c r="D116" s="2" t="s">
         <v>250</v>
@@ -6208,16 +6208,16 @@
         <v>251</v>
       </c>
       <c r="F116" s="2" t="s">
-        <v>51</v>
+        <v>47</v>
       </c>
       <c r="G116" s="2" t="s">
-        <v>52</v>
+        <v>48</v>
       </c>
       <c r="H116" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I116" s="2" t="n">
-        <v>94.92</v>
+        <v>94.88</v>
       </c>
       <c r="J116" s="2" t="s">
         <v>16</v>
@@ -6228,10 +6228,10 @@
         <v>2022</v>
       </c>
       <c r="B117" s="2" t="n">
-        <v>5</v>
+        <v>13</v>
       </c>
       <c r="C117" s="2" t="s">
-        <v>58</v>
+        <v>160</v>
       </c>
       <c r="D117" s="2" t="s">
         <v>252</v>
@@ -6240,16 +6240,16 @@
         <v>253</v>
       </c>
       <c r="F117" s="2" t="s">
-        <v>51</v>
+        <v>47</v>
       </c>
       <c r="G117" s="2" t="s">
-        <v>52</v>
+        <v>48</v>
       </c>
       <c r="H117" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I117" s="2" t="n">
-        <v>94.88</v>
+        <v>94.87</v>
       </c>
       <c r="J117" s="2" t="s">
         <v>16</v>
@@ -6263,7 +6263,7 @@
         <v>13</v>
       </c>
       <c r="C118" s="2" t="s">
-        <v>162</v>
+        <v>160</v>
       </c>
       <c r="D118" s="2" t="s">
         <v>254</v>
@@ -6272,16 +6272,16 @@
         <v>255</v>
       </c>
       <c r="F118" s="2" t="s">
-        <v>51</v>
+        <v>47</v>
       </c>
       <c r="G118" s="2" t="s">
-        <v>52</v>
+        <v>48</v>
       </c>
       <c r="H118" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I118" s="2" t="n">
-        <v>94.87</v>
+        <v>94.84</v>
       </c>
       <c r="J118" s="2" t="s">
         <v>16</v>
@@ -6292,10 +6292,10 @@
         <v>2022</v>
       </c>
       <c r="B119" s="2" t="n">
-        <v>13</v>
+        <v>6</v>
       </c>
       <c r="C119" s="2" t="s">
-        <v>162</v>
+        <v>57</v>
       </c>
       <c r="D119" s="2" t="s">
         <v>256</v>
@@ -6304,16 +6304,16 @@
         <v>257</v>
       </c>
       <c r="F119" s="2" t="s">
-        <v>51</v>
+        <v>47</v>
       </c>
       <c r="G119" s="2" t="s">
-        <v>52</v>
+        <v>48</v>
       </c>
       <c r="H119" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I119" s="2" t="n">
-        <v>94.84</v>
+        <v>94.78</v>
       </c>
       <c r="J119" s="2" t="s">
         <v>16</v>
@@ -6327,7 +6327,7 @@
         <v>6</v>
       </c>
       <c r="C120" s="2" t="s">
-        <v>61</v>
+        <v>57</v>
       </c>
       <c r="D120" s="2" t="s">
         <v>258</v>
@@ -6336,16 +6336,16 @@
         <v>259</v>
       </c>
       <c r="F120" s="2" t="s">
-        <v>51</v>
+        <v>47</v>
       </c>
       <c r="G120" s="2" t="s">
-        <v>52</v>
+        <v>48</v>
       </c>
       <c r="H120" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I120" s="2" t="n">
-        <v>94.78</v>
+        <v>94.77</v>
       </c>
       <c r="J120" s="2" t="s">
         <v>16</v>
@@ -6356,10 +6356,10 @@
         <v>2022</v>
       </c>
       <c r="B121" s="2" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C121" s="2" t="s">
-        <v>61</v>
+        <v>54</v>
       </c>
       <c r="D121" s="2" t="s">
         <v>260</v>
@@ -6368,16 +6368,16 @@
         <v>261</v>
       </c>
       <c r="F121" s="2" t="s">
-        <v>51</v>
+        <v>47</v>
       </c>
       <c r="G121" s="2" t="s">
-        <v>52</v>
+        <v>48</v>
       </c>
       <c r="H121" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I121" s="2" t="n">
-        <v>94.77</v>
+        <v>94.7</v>
       </c>
       <c r="J121" s="2" t="s">
         <v>16</v>
@@ -6388,10 +6388,10 @@
         <v>2022</v>
       </c>
       <c r="B122" s="2" t="n">
-        <v>5</v>
+        <v>13</v>
       </c>
       <c r="C122" s="2" t="s">
-        <v>58</v>
+        <v>160</v>
       </c>
       <c r="D122" s="2" t="s">
         <v>262</v>
@@ -6400,16 +6400,16 @@
         <v>263</v>
       </c>
       <c r="F122" s="2" t="s">
-        <v>51</v>
+        <v>47</v>
       </c>
       <c r="G122" s="2" t="s">
-        <v>52</v>
+        <v>48</v>
       </c>
       <c r="H122" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I122" s="2" t="n">
-        <v>94.7</v>
+        <v>94.69</v>
       </c>
       <c r="J122" s="2" t="s">
         <v>16</v>
@@ -6423,7 +6423,7 @@
         <v>13</v>
       </c>
       <c r="C123" s="2" t="s">
-        <v>162</v>
+        <v>160</v>
       </c>
       <c r="D123" s="2" t="s">
         <v>264</v>
@@ -6432,10 +6432,10 @@
         <v>265</v>
       </c>
       <c r="F123" s="2" t="s">
-        <v>51</v>
+        <v>47</v>
       </c>
       <c r="G123" s="2" t="s">
-        <v>52</v>
+        <v>48</v>
       </c>
       <c r="H123" s="2" t="s">
         <v>15</v>
@@ -6455,7 +6455,7 @@
         <v>13</v>
       </c>
       <c r="C124" s="2" t="s">
-        <v>162</v>
+        <v>160</v>
       </c>
       <c r="D124" s="2" t="s">
         <v>266</v>
@@ -6464,16 +6464,16 @@
         <v>267</v>
       </c>
       <c r="F124" s="2" t="s">
-        <v>51</v>
+        <v>47</v>
       </c>
       <c r="G124" s="2" t="s">
-        <v>52</v>
+        <v>48</v>
       </c>
       <c r="H124" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I124" s="2" t="n">
-        <v>94.69</v>
+        <v>94.68</v>
       </c>
       <c r="J124" s="2" t="s">
         <v>16</v>
@@ -6487,7 +6487,7 @@
         <v>13</v>
       </c>
       <c r="C125" s="2" t="s">
-        <v>162</v>
+        <v>160</v>
       </c>
       <c r="D125" s="2" t="s">
         <v>268</v>
@@ -6496,16 +6496,16 @@
         <v>269</v>
       </c>
       <c r="F125" s="2" t="s">
-        <v>51</v>
+        <v>47</v>
       </c>
       <c r="G125" s="2" t="s">
-        <v>52</v>
+        <v>48</v>
       </c>
       <c r="H125" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I125" s="2" t="n">
-        <v>94.68</v>
+        <v>94.6</v>
       </c>
       <c r="J125" s="2" t="s">
         <v>16</v>
@@ -6519,7 +6519,7 @@
         <v>13</v>
       </c>
       <c r="C126" s="2" t="s">
-        <v>162</v>
+        <v>160</v>
       </c>
       <c r="D126" s="2" t="s">
         <v>270</v>
@@ -6528,16 +6528,16 @@
         <v>271</v>
       </c>
       <c r="F126" s="2" t="s">
-        <v>51</v>
+        <v>47</v>
       </c>
       <c r="G126" s="2" t="s">
-        <v>52</v>
+        <v>48</v>
       </c>
       <c r="H126" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I126" s="2" t="n">
-        <v>94.6</v>
+        <v>94.58</v>
       </c>
       <c r="J126" s="2" t="s">
         <v>16</v>
@@ -6551,7 +6551,7 @@
         <v>13</v>
       </c>
       <c r="C127" s="2" t="s">
-        <v>162</v>
+        <v>160</v>
       </c>
       <c r="D127" s="2" t="s">
         <v>272</v>
@@ -6560,10 +6560,10 @@
         <v>273</v>
       </c>
       <c r="F127" s="2" t="s">
-        <v>51</v>
+        <v>47</v>
       </c>
       <c r="G127" s="2" t="s">
-        <v>52</v>
+        <v>48</v>
       </c>
       <c r="H127" s="2" t="s">
         <v>15</v>
@@ -6583,7 +6583,7 @@
         <v>13</v>
       </c>
       <c r="C128" s="2" t="s">
-        <v>162</v>
+        <v>160</v>
       </c>
       <c r="D128" s="2" t="s">
         <v>274</v>
@@ -6592,16 +6592,16 @@
         <v>275</v>
       </c>
       <c r="F128" s="2" t="s">
-        <v>51</v>
+        <v>47</v>
       </c>
       <c r="G128" s="2" t="s">
-        <v>52</v>
+        <v>48</v>
       </c>
       <c r="H128" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I128" s="2" t="n">
-        <v>94.58</v>
+        <v>94.57</v>
       </c>
       <c r="J128" s="2" t="s">
         <v>16</v>
@@ -6615,7 +6615,7 @@
         <v>13</v>
       </c>
       <c r="C129" s="2" t="s">
-        <v>162</v>
+        <v>160</v>
       </c>
       <c r="D129" s="2" t="s">
         <v>276</v>
@@ -6624,16 +6624,16 @@
         <v>277</v>
       </c>
       <c r="F129" s="2" t="s">
-        <v>51</v>
+        <v>47</v>
       </c>
       <c r="G129" s="2" t="s">
-        <v>52</v>
+        <v>48</v>
       </c>
       <c r="H129" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I129" s="2" t="n">
-        <v>94.57</v>
+        <v>94.55</v>
       </c>
       <c r="J129" s="2" t="s">
         <v>16</v>
@@ -6644,10 +6644,10 @@
         <v>2022</v>
       </c>
       <c r="B130" s="2" t="n">
-        <v>13</v>
+        <v>5</v>
       </c>
       <c r="C130" s="2" t="s">
-        <v>162</v>
+        <v>54</v>
       </c>
       <c r="D130" s="2" t="s">
         <v>278</v>
@@ -6656,16 +6656,16 @@
         <v>279</v>
       </c>
       <c r="F130" s="2" t="s">
-        <v>51</v>
+        <v>47</v>
       </c>
       <c r="G130" s="2" t="s">
-        <v>52</v>
+        <v>48</v>
       </c>
       <c r="H130" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I130" s="2" t="n">
-        <v>94.55</v>
+        <v>94.53</v>
       </c>
       <c r="J130" s="2" t="s">
         <v>16</v>
@@ -6676,10 +6676,10 @@
         <v>2022</v>
       </c>
       <c r="B131" s="2" t="n">
-        <v>5</v>
+        <v>13</v>
       </c>
       <c r="C131" s="2" t="s">
-        <v>58</v>
+        <v>160</v>
       </c>
       <c r="D131" s="2" t="s">
         <v>280</v>
@@ -6688,16 +6688,16 @@
         <v>281</v>
       </c>
       <c r="F131" s="2" t="s">
-        <v>51</v>
+        <v>47</v>
       </c>
       <c r="G131" s="2" t="s">
-        <v>52</v>
+        <v>48</v>
       </c>
       <c r="H131" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I131" s="2" t="n">
-        <v>94.53</v>
+        <v>94.51</v>
       </c>
       <c r="J131" s="2" t="s">
         <v>16</v>
@@ -6711,7 +6711,7 @@
         <v>13</v>
       </c>
       <c r="C132" s="2" t="s">
-        <v>162</v>
+        <v>160</v>
       </c>
       <c r="D132" s="2" t="s">
         <v>282</v>
@@ -6720,16 +6720,16 @@
         <v>283</v>
       </c>
       <c r="F132" s="2" t="s">
-        <v>51</v>
+        <v>47</v>
       </c>
       <c r="G132" s="2" t="s">
-        <v>52</v>
+        <v>48</v>
       </c>
       <c r="H132" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I132" s="2" t="n">
-        <v>94.51</v>
+        <v>94.49</v>
       </c>
       <c r="J132" s="2" t="s">
         <v>16</v>
@@ -6740,10 +6740,10 @@
         <v>2022</v>
       </c>
       <c r="B133" s="2" t="n">
-        <v>13</v>
+        <v>6</v>
       </c>
       <c r="C133" s="2" t="s">
-        <v>162</v>
+        <v>57</v>
       </c>
       <c r="D133" s="2" t="s">
         <v>284</v>
@@ -6752,16 +6752,16 @@
         <v>285</v>
       </c>
       <c r="F133" s="2" t="s">
-        <v>51</v>
+        <v>47</v>
       </c>
       <c r="G133" s="2" t="s">
-        <v>52</v>
+        <v>48</v>
       </c>
       <c r="H133" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I133" s="2" t="n">
-        <v>94.49</v>
+        <v>94.47</v>
       </c>
       <c r="J133" s="2" t="s">
         <v>16</v>
@@ -6772,10 +6772,10 @@
         <v>2022</v>
       </c>
       <c r="B134" s="2" t="n">
-        <v>6</v>
+        <v>13</v>
       </c>
       <c r="C134" s="2" t="s">
-        <v>61</v>
+        <v>160</v>
       </c>
       <c r="D134" s="2" t="s">
         <v>286</v>
@@ -6784,16 +6784,16 @@
         <v>287</v>
       </c>
       <c r="F134" s="2" t="s">
-        <v>51</v>
+        <v>47</v>
       </c>
       <c r="G134" s="2" t="s">
-        <v>52</v>
+        <v>48</v>
       </c>
       <c r="H134" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I134" s="2" t="n">
-        <v>94.47</v>
+        <v>94.42</v>
       </c>
       <c r="J134" s="2" t="s">
         <v>16</v>
@@ -6804,10 +6804,10 @@
         <v>2022</v>
       </c>
       <c r="B135" s="2" t="n">
-        <v>13</v>
+        <v>5</v>
       </c>
       <c r="C135" s="2" t="s">
-        <v>162</v>
+        <v>54</v>
       </c>
       <c r="D135" s="2" t="s">
         <v>288</v>
@@ -6816,16 +6816,16 @@
         <v>289</v>
       </c>
       <c r="F135" s="2" t="s">
-        <v>51</v>
+        <v>47</v>
       </c>
       <c r="G135" s="2" t="s">
-        <v>52</v>
+        <v>48</v>
       </c>
       <c r="H135" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I135" s="2" t="n">
-        <v>94.42</v>
+        <v>94.41</v>
       </c>
       <c r="J135" s="2" t="s">
         <v>16</v>
@@ -6836,10 +6836,10 @@
         <v>2022</v>
       </c>
       <c r="B136" s="2" t="n">
-        <v>5</v>
+        <v>16</v>
       </c>
       <c r="C136" s="2" t="s">
-        <v>58</v>
+        <v>49</v>
       </c>
       <c r="D136" s="2" t="s">
         <v>290</v>
@@ -6848,16 +6848,16 @@
         <v>291</v>
       </c>
       <c r="F136" s="2" t="s">
-        <v>51</v>
+        <v>47</v>
       </c>
       <c r="G136" s="2" t="s">
-        <v>52</v>
+        <v>48</v>
       </c>
       <c r="H136" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I136" s="2" t="n">
-        <v>94.41</v>
+        <v>94.38</v>
       </c>
       <c r="J136" s="2" t="s">
         <v>16</v>
@@ -6868,10 +6868,10 @@
         <v>2022</v>
       </c>
       <c r="B137" s="2" t="n">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="C137" s="2" t="s">
-        <v>53</v>
+        <v>160</v>
       </c>
       <c r="D137" s="2" t="s">
         <v>292</v>
@@ -6880,16 +6880,16 @@
         <v>293</v>
       </c>
       <c r="F137" s="2" t="s">
-        <v>51</v>
+        <v>47</v>
       </c>
       <c r="G137" s="2" t="s">
-        <v>52</v>
+        <v>48</v>
       </c>
       <c r="H137" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I137" s="2" t="n">
-        <v>94.38</v>
+        <v>94.35</v>
       </c>
       <c r="J137" s="2" t="s">
         <v>16</v>
@@ -6903,7 +6903,7 @@
         <v>13</v>
       </c>
       <c r="C138" s="2" t="s">
-        <v>162</v>
+        <v>160</v>
       </c>
       <c r="D138" s="2" t="s">
         <v>294</v>
@@ -6912,16 +6912,16 @@
         <v>295</v>
       </c>
       <c r="F138" s="2" t="s">
-        <v>51</v>
+        <v>47</v>
       </c>
       <c r="G138" s="2" t="s">
-        <v>52</v>
+        <v>48</v>
       </c>
       <c r="H138" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I138" s="2" t="n">
-        <v>94.35</v>
+        <v>94.32</v>
       </c>
       <c r="J138" s="2" t="s">
         <v>16</v>
@@ -6935,7 +6935,7 @@
         <v>13</v>
       </c>
       <c r="C139" s="2" t="s">
-        <v>162</v>
+        <v>160</v>
       </c>
       <c r="D139" s="2" t="s">
         <v>296</v>
@@ -6944,16 +6944,16 @@
         <v>297</v>
       </c>
       <c r="F139" s="2" t="s">
-        <v>51</v>
+        <v>47</v>
       </c>
       <c r="G139" s="2" t="s">
-        <v>52</v>
+        <v>48</v>
       </c>
       <c r="H139" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I139" s="2" t="n">
-        <v>94.32</v>
+        <v>94.26</v>
       </c>
       <c r="J139" s="2" t="s">
         <v>16</v>
@@ -6967,7 +6967,7 @@
         <v>13</v>
       </c>
       <c r="C140" s="2" t="s">
-        <v>162</v>
+        <v>160</v>
       </c>
       <c r="D140" s="2" t="s">
         <v>298</v>
@@ -6976,16 +6976,16 @@
         <v>299</v>
       </c>
       <c r="F140" s="2" t="s">
-        <v>51</v>
+        <v>47</v>
       </c>
       <c r="G140" s="2" t="s">
-        <v>52</v>
+        <v>48</v>
       </c>
       <c r="H140" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I140" s="2" t="n">
-        <v>94.26</v>
+        <v>94.24</v>
       </c>
       <c r="J140" s="2" t="s">
         <v>16</v>
@@ -6996,10 +6996,10 @@
         <v>2022</v>
       </c>
       <c r="B141" s="2" t="n">
-        <v>13</v>
+        <v>6</v>
       </c>
       <c r="C141" s="2" t="s">
-        <v>162</v>
+        <v>57</v>
       </c>
       <c r="D141" s="2" t="s">
         <v>300</v>
@@ -7008,16 +7008,16 @@
         <v>301</v>
       </c>
       <c r="F141" s="2" t="s">
-        <v>51</v>
+        <v>47</v>
       </c>
       <c r="G141" s="2" t="s">
-        <v>52</v>
+        <v>48</v>
       </c>
       <c r="H141" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I141" s="2" t="n">
-        <v>94.24</v>
+        <v>94.23</v>
       </c>
       <c r="J141" s="2" t="s">
         <v>16</v>
@@ -7028,10 +7028,10 @@
         <v>2022</v>
       </c>
       <c r="B142" s="2" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C142" s="2" t="s">
-        <v>61</v>
+        <v>54</v>
       </c>
       <c r="D142" s="2" t="s">
         <v>302</v>
@@ -7040,16 +7040,16 @@
         <v>303</v>
       </c>
       <c r="F142" s="2" t="s">
-        <v>51</v>
+        <v>47</v>
       </c>
       <c r="G142" s="2" t="s">
-        <v>52</v>
+        <v>48</v>
       </c>
       <c r="H142" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I142" s="2" t="n">
-        <v>94.23</v>
+        <v>94.22</v>
       </c>
       <c r="J142" s="2" t="s">
         <v>16</v>
@@ -7063,7 +7063,7 @@
         <v>5</v>
       </c>
       <c r="C143" s="2" t="s">
-        <v>58</v>
+        <v>54</v>
       </c>
       <c r="D143" s="2" t="s">
         <v>304</v>
@@ -7072,16 +7072,16 @@
         <v>305</v>
       </c>
       <c r="F143" s="2" t="s">
-        <v>51</v>
+        <v>47</v>
       </c>
       <c r="G143" s="2" t="s">
-        <v>52</v>
+        <v>48</v>
       </c>
       <c r="H143" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I143" s="2" t="n">
-        <v>94.22</v>
+        <v>94.18</v>
       </c>
       <c r="J143" s="2" t="s">
         <v>16</v>
@@ -7095,7 +7095,7 @@
         <v>5</v>
       </c>
       <c r="C144" s="2" t="s">
-        <v>58</v>
+        <v>54</v>
       </c>
       <c r="D144" s="2" t="s">
         <v>306</v>
@@ -7104,16 +7104,16 @@
         <v>307</v>
       </c>
       <c r="F144" s="2" t="s">
-        <v>51</v>
+        <v>47</v>
       </c>
       <c r="G144" s="2" t="s">
-        <v>52</v>
+        <v>48</v>
       </c>
       <c r="H144" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I144" s="2" t="n">
-        <v>94.18</v>
+        <v>94.14</v>
       </c>
       <c r="J144" s="2" t="s">
         <v>16</v>
@@ -7124,10 +7124,10 @@
         <v>2022</v>
       </c>
       <c r="B145" s="2" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="C145" s="2" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="D145" s="2" t="s">
         <v>308</v>
@@ -7136,10 +7136,10 @@
         <v>309</v>
       </c>
       <c r="F145" s="2" t="s">
-        <v>51</v>
+        <v>47</v>
       </c>
       <c r="G145" s="2" t="s">
-        <v>52</v>
+        <v>48</v>
       </c>
       <c r="H145" s="2" t="s">
         <v>15</v>
@@ -7156,10 +7156,10 @@
         <v>2022</v>
       </c>
       <c r="B146" s="2" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C146" s="2" t="s">
-        <v>61</v>
+        <v>54</v>
       </c>
       <c r="D146" s="2" t="s">
         <v>310</v>
@@ -7168,16 +7168,16 @@
         <v>311</v>
       </c>
       <c r="F146" s="2" t="s">
-        <v>51</v>
+        <v>47</v>
       </c>
       <c r="G146" s="2" t="s">
-        <v>52</v>
+        <v>48</v>
       </c>
       <c r="H146" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I146" s="2" t="n">
-        <v>94.14</v>
+        <v>94.03</v>
       </c>
       <c r="J146" s="2" t="s">
         <v>16</v>
@@ -7188,10 +7188,10 @@
         <v>2022</v>
       </c>
       <c r="B147" s="2" t="n">
-        <v>5</v>
+        <v>13</v>
       </c>
       <c r="C147" s="2" t="s">
-        <v>58</v>
+        <v>160</v>
       </c>
       <c r="D147" s="2" t="s">
         <v>312</v>
@@ -7200,16 +7200,16 @@
         <v>313</v>
       </c>
       <c r="F147" s="2" t="s">
-        <v>51</v>
+        <v>47</v>
       </c>
       <c r="G147" s="2" t="s">
-        <v>52</v>
+        <v>48</v>
       </c>
       <c r="H147" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I147" s="2" t="n">
-        <v>94.03</v>
+        <v>94.02</v>
       </c>
       <c r="J147" s="2" t="s">
         <v>16</v>
@@ -7220,10 +7220,10 @@
         <v>2022</v>
       </c>
       <c r="B148" s="2" t="n">
-        <v>13</v>
+        <v>5</v>
       </c>
       <c r="C148" s="2" t="s">
-        <v>162</v>
+        <v>54</v>
       </c>
       <c r="D148" s="2" t="s">
         <v>314</v>
@@ -7232,16 +7232,16 @@
         <v>315</v>
       </c>
       <c r="F148" s="2" t="s">
-        <v>51</v>
+        <v>47</v>
       </c>
       <c r="G148" s="2" t="s">
-        <v>52</v>
+        <v>48</v>
       </c>
       <c r="H148" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I148" s="2" t="n">
-        <v>94.02</v>
+        <v>93.97</v>
       </c>
       <c r="J148" s="2" t="s">
         <v>16</v>
@@ -7252,10 +7252,10 @@
         <v>2022</v>
       </c>
       <c r="B149" s="2" t="n">
-        <v>5</v>
+        <v>13</v>
       </c>
       <c r="C149" s="2" t="s">
-        <v>58</v>
+        <v>160</v>
       </c>
       <c r="D149" s="2" t="s">
         <v>316</v>
@@ -7264,16 +7264,16 @@
         <v>317</v>
       </c>
       <c r="F149" s="2" t="s">
-        <v>51</v>
+        <v>47</v>
       </c>
       <c r="G149" s="2" t="s">
-        <v>52</v>
+        <v>48</v>
       </c>
       <c r="H149" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I149" s="2" t="n">
-        <v>93.97</v>
+        <v>93.86</v>
       </c>
       <c r="J149" s="2" t="s">
         <v>16</v>
@@ -7287,7 +7287,7 @@
         <v>13</v>
       </c>
       <c r="C150" s="2" t="s">
-        <v>162</v>
+        <v>160</v>
       </c>
       <c r="D150" s="2" t="s">
         <v>318</v>
@@ -7296,16 +7296,16 @@
         <v>319</v>
       </c>
       <c r="F150" s="2" t="s">
-        <v>51</v>
+        <v>47</v>
       </c>
       <c r="G150" s="2" t="s">
-        <v>52</v>
+        <v>48</v>
       </c>
       <c r="H150" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I150" s="2" t="n">
-        <v>93.86</v>
+        <v>93.84</v>
       </c>
       <c r="J150" s="2" t="s">
         <v>16</v>
@@ -7316,10 +7316,10 @@
         <v>2022</v>
       </c>
       <c r="B151" s="2" t="n">
-        <v>13</v>
+        <v>5</v>
       </c>
       <c r="C151" s="2" t="s">
-        <v>162</v>
+        <v>54</v>
       </c>
       <c r="D151" s="2" t="s">
         <v>320</v>
@@ -7328,16 +7328,16 @@
         <v>321</v>
       </c>
       <c r="F151" s="2" t="s">
-        <v>51</v>
+        <v>47</v>
       </c>
       <c r="G151" s="2" t="s">
-        <v>52</v>
+        <v>48</v>
       </c>
       <c r="H151" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I151" s="2" t="n">
-        <v>93.84</v>
+        <v>93.66</v>
       </c>
       <c r="J151" s="2" t="s">
         <v>16</v>
@@ -7351,7 +7351,7 @@
         <v>5</v>
       </c>
       <c r="C152" s="2" t="s">
-        <v>58</v>
+        <v>54</v>
       </c>
       <c r="D152" s="2" t="s">
         <v>322</v>
@@ -7360,16 +7360,16 @@
         <v>323</v>
       </c>
       <c r="F152" s="2" t="s">
-        <v>51</v>
+        <v>47</v>
       </c>
       <c r="G152" s="2" t="s">
-        <v>52</v>
+        <v>48</v>
       </c>
       <c r="H152" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I152" s="2" t="n">
-        <v>93.66</v>
+        <v>93.52</v>
       </c>
       <c r="J152" s="2" t="s">
         <v>16</v>
@@ -7383,7 +7383,7 @@
         <v>5</v>
       </c>
       <c r="C153" s="2" t="s">
-        <v>58</v>
+        <v>54</v>
       </c>
       <c r="D153" s="2" t="s">
         <v>324</v>
@@ -7392,16 +7392,16 @@
         <v>325</v>
       </c>
       <c r="F153" s="2" t="s">
-        <v>51</v>
+        <v>47</v>
       </c>
       <c r="G153" s="2" t="s">
-        <v>52</v>
+        <v>48</v>
       </c>
       <c r="H153" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I153" s="2" t="n">
-        <v>93.52</v>
+        <v>93.39</v>
       </c>
       <c r="J153" s="2" t="s">
         <v>16</v>
@@ -7412,10 +7412,10 @@
         <v>2022</v>
       </c>
       <c r="B154" s="2" t="n">
-        <v>5</v>
+        <v>13</v>
       </c>
       <c r="C154" s="2" t="s">
-        <v>58</v>
+        <v>160</v>
       </c>
       <c r="D154" s="2" t="s">
         <v>326</v>
@@ -7424,16 +7424,16 @@
         <v>327</v>
       </c>
       <c r="F154" s="2" t="s">
-        <v>51</v>
+        <v>47</v>
       </c>
       <c r="G154" s="2" t="s">
-        <v>52</v>
+        <v>48</v>
       </c>
       <c r="H154" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I154" s="2" t="n">
-        <v>93.39</v>
+        <v>93.31</v>
       </c>
       <c r="J154" s="2" t="s">
         <v>16</v>
@@ -7447,7 +7447,7 @@
         <v>13</v>
       </c>
       <c r="C155" s="2" t="s">
-        <v>162</v>
+        <v>160</v>
       </c>
       <c r="D155" s="2" t="s">
         <v>328</v>
@@ -7456,16 +7456,16 @@
         <v>329</v>
       </c>
       <c r="F155" s="2" t="s">
-        <v>51</v>
+        <v>47</v>
       </c>
       <c r="G155" s="2" t="s">
-        <v>52</v>
+        <v>48</v>
       </c>
       <c r="H155" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I155" s="2" t="n">
-        <v>93.31</v>
+        <v>93.3</v>
       </c>
       <c r="J155" s="2" t="s">
         <v>16</v>
@@ -7479,7 +7479,7 @@
         <v>13</v>
       </c>
       <c r="C156" s="2" t="s">
-        <v>162</v>
+        <v>160</v>
       </c>
       <c r="D156" s="2" t="s">
         <v>330</v>
@@ -7488,16 +7488,16 @@
         <v>331</v>
       </c>
       <c r="F156" s="2" t="s">
-        <v>51</v>
+        <v>47</v>
       </c>
       <c r="G156" s="2" t="s">
-        <v>52</v>
+        <v>48</v>
       </c>
       <c r="H156" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I156" s="2" t="n">
-        <v>93.3</v>
+        <v>93.25</v>
       </c>
       <c r="J156" s="2" t="s">
         <v>16</v>
@@ -7511,7 +7511,7 @@
         <v>13</v>
       </c>
       <c r="C157" s="2" t="s">
-        <v>162</v>
+        <v>160</v>
       </c>
       <c r="D157" s="2" t="s">
         <v>332</v>
@@ -7520,16 +7520,16 @@
         <v>333</v>
       </c>
       <c r="F157" s="2" t="s">
-        <v>51</v>
+        <v>47</v>
       </c>
       <c r="G157" s="2" t="s">
-        <v>52</v>
+        <v>48</v>
       </c>
       <c r="H157" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I157" s="2" t="n">
-        <v>93.25</v>
+        <v>93.04</v>
       </c>
       <c r="J157" s="2" t="s">
         <v>16</v>
@@ -7540,10 +7540,10 @@
         <v>2022</v>
       </c>
       <c r="B158" s="2" t="n">
-        <v>13</v>
+        <v>5</v>
       </c>
       <c r="C158" s="2" t="s">
-        <v>162</v>
+        <v>54</v>
       </c>
       <c r="D158" s="2" t="s">
         <v>334</v>
@@ -7552,16 +7552,16 @@
         <v>335</v>
       </c>
       <c r="F158" s="2" t="s">
-        <v>51</v>
+        <v>47</v>
       </c>
       <c r="G158" s="2" t="s">
-        <v>52</v>
+        <v>48</v>
       </c>
       <c r="H158" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I158" s="2" t="n">
-        <v>93.04</v>
+        <v>93.01</v>
       </c>
       <c r="J158" s="2" t="s">
         <v>16</v>
@@ -7575,7 +7575,7 @@
         <v>5</v>
       </c>
       <c r="C159" s="2" t="s">
-        <v>58</v>
+        <v>54</v>
       </c>
       <c r="D159" s="2" t="s">
         <v>336</v>
@@ -7584,16 +7584,16 @@
         <v>337</v>
       </c>
       <c r="F159" s="2" t="s">
-        <v>51</v>
+        <v>47</v>
       </c>
       <c r="G159" s="2" t="s">
-        <v>52</v>
+        <v>48</v>
       </c>
       <c r="H159" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I159" s="2" t="n">
-        <v>93.01</v>
+        <v>92.99</v>
       </c>
       <c r="J159" s="2" t="s">
         <v>16</v>
@@ -7604,10 +7604,10 @@
         <v>2022</v>
       </c>
       <c r="B160" s="2" t="n">
-        <v>5</v>
+        <v>13</v>
       </c>
       <c r="C160" s="2" t="s">
-        <v>58</v>
+        <v>160</v>
       </c>
       <c r="D160" s="2" t="s">
         <v>338</v>
@@ -7616,16 +7616,16 @@
         <v>339</v>
       </c>
       <c r="F160" s="2" t="s">
-        <v>51</v>
+        <v>47</v>
       </c>
       <c r="G160" s="2" t="s">
-        <v>52</v>
+        <v>48</v>
       </c>
       <c r="H160" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I160" s="2" t="n">
-        <v>92.99</v>
+        <v>92.68</v>
       </c>
       <c r="J160" s="2" t="s">
         <v>16</v>
@@ -7639,7 +7639,7 @@
         <v>13</v>
       </c>
       <c r="C161" s="2" t="s">
-        <v>162</v>
+        <v>160</v>
       </c>
       <c r="D161" s="2" t="s">
         <v>340</v>
@@ -7648,16 +7648,16 @@
         <v>341</v>
       </c>
       <c r="F161" s="2" t="s">
-        <v>51</v>
+        <v>47</v>
       </c>
       <c r="G161" s="2" t="s">
-        <v>52</v>
+        <v>48</v>
       </c>
       <c r="H161" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I161" s="2" t="n">
-        <v>92.68</v>
+        <v>92.62</v>
       </c>
       <c r="J161" s="2" t="s">
         <v>16</v>
@@ -7671,7 +7671,7 @@
         <v>13</v>
       </c>
       <c r="C162" s="2" t="s">
-        <v>162</v>
+        <v>160</v>
       </c>
       <c r="D162" s="2" t="s">
         <v>342</v>
@@ -7680,16 +7680,16 @@
         <v>343</v>
       </c>
       <c r="F162" s="2" t="s">
-        <v>51</v>
+        <v>47</v>
       </c>
       <c r="G162" s="2" t="s">
-        <v>52</v>
+        <v>48</v>
       </c>
       <c r="H162" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I162" s="2" t="n">
-        <v>92.62</v>
+        <v>92.58</v>
       </c>
       <c r="J162" s="2" t="s">
         <v>16</v>
@@ -7703,7 +7703,7 @@
         <v>13</v>
       </c>
       <c r="C163" s="2" t="s">
-        <v>162</v>
+        <v>160</v>
       </c>
       <c r="D163" s="2" t="s">
         <v>344</v>
@@ -7712,16 +7712,16 @@
         <v>345</v>
       </c>
       <c r="F163" s="2" t="s">
-        <v>51</v>
+        <v>47</v>
       </c>
       <c r="G163" s="2" t="s">
-        <v>52</v>
+        <v>48</v>
       </c>
       <c r="H163" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I163" s="2" t="n">
-        <v>92.58</v>
+        <v>92.54</v>
       </c>
       <c r="J163" s="2" t="s">
         <v>16</v>
@@ -7732,10 +7732,10 @@
         <v>2022</v>
       </c>
       <c r="B164" s="2" t="n">
-        <v>13</v>
+        <v>5</v>
       </c>
       <c r="C164" s="2" t="s">
-        <v>162</v>
+        <v>54</v>
       </c>
       <c r="D164" s="2" t="s">
         <v>346</v>
@@ -7744,16 +7744,16 @@
         <v>347</v>
       </c>
       <c r="F164" s="2" t="s">
-        <v>51</v>
+        <v>47</v>
       </c>
       <c r="G164" s="2" t="s">
-        <v>52</v>
+        <v>48</v>
       </c>
       <c r="H164" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I164" s="2" t="n">
-        <v>92.54</v>
+        <v>92.03</v>
       </c>
       <c r="J164" s="2" t="s">
         <v>16</v>
@@ -7767,7 +7767,7 @@
         <v>5</v>
       </c>
       <c r="C165" s="2" t="s">
-        <v>58</v>
+        <v>54</v>
       </c>
       <c r="D165" s="2" t="s">
         <v>348</v>
@@ -7776,16 +7776,16 @@
         <v>349</v>
       </c>
       <c r="F165" s="2" t="s">
-        <v>51</v>
+        <v>47</v>
       </c>
       <c r="G165" s="2" t="s">
-        <v>52</v>
+        <v>48</v>
       </c>
       <c r="H165" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I165" s="2" t="n">
-        <v>92.03</v>
+        <v>91.91</v>
       </c>
       <c r="J165" s="2" t="s">
         <v>16</v>
@@ -7796,10 +7796,10 @@
         <v>2022</v>
       </c>
       <c r="B166" s="2" t="n">
-        <v>5</v>
+        <v>13</v>
       </c>
       <c r="C166" s="2" t="s">
-        <v>58</v>
+        <v>160</v>
       </c>
       <c r="D166" s="2" t="s">
         <v>350</v>
@@ -7808,16 +7808,16 @@
         <v>351</v>
       </c>
       <c r="F166" s="2" t="s">
-        <v>51</v>
+        <v>47</v>
       </c>
       <c r="G166" s="2" t="s">
-        <v>52</v>
+        <v>48</v>
       </c>
       <c r="H166" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I166" s="2" t="n">
-        <v>91.91</v>
+        <v>91.68</v>
       </c>
       <c r="J166" s="2" t="s">
         <v>16</v>
@@ -7831,7 +7831,7 @@
         <v>13</v>
       </c>
       <c r="C167" s="2" t="s">
-        <v>162</v>
+        <v>160</v>
       </c>
       <c r="D167" s="2" t="s">
         <v>352</v>
@@ -7840,16 +7840,16 @@
         <v>353</v>
       </c>
       <c r="F167" s="2" t="s">
-        <v>51</v>
+        <v>47</v>
       </c>
       <c r="G167" s="2" t="s">
-        <v>52</v>
+        <v>48</v>
       </c>
       <c r="H167" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I167" s="2" t="n">
-        <v>91.68</v>
+        <v>91.35</v>
       </c>
       <c r="J167" s="2" t="s">
         <v>16</v>
@@ -7863,7 +7863,7 @@
         <v>13</v>
       </c>
       <c r="C168" s="2" t="s">
-        <v>162</v>
+        <v>160</v>
       </c>
       <c r="D168" s="2" t="s">
         <v>354</v>
@@ -7872,16 +7872,16 @@
         <v>355</v>
       </c>
       <c r="F168" s="2" t="s">
-        <v>51</v>
+        <v>47</v>
       </c>
       <c r="G168" s="2" t="s">
-        <v>52</v>
+        <v>48</v>
       </c>
       <c r="H168" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I168" s="2" t="n">
-        <v>91.35</v>
+        <v>91.28</v>
       </c>
       <c r="J168" s="2" t="s">
         <v>16</v>
@@ -7895,7 +7895,7 @@
         <v>13</v>
       </c>
       <c r="C169" s="2" t="s">
-        <v>162</v>
+        <v>160</v>
       </c>
       <c r="D169" s="2" t="s">
         <v>356</v>
@@ -7904,16 +7904,16 @@
         <v>357</v>
       </c>
       <c r="F169" s="2" t="s">
-        <v>51</v>
+        <v>47</v>
       </c>
       <c r="G169" s="2" t="s">
-        <v>52</v>
+        <v>48</v>
       </c>
       <c r="H169" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I169" s="2" t="n">
-        <v>91.28</v>
+        <v>90.99</v>
       </c>
       <c r="J169" s="2" t="s">
         <v>16</v>
@@ -7924,10 +7924,10 @@
         <v>2022</v>
       </c>
       <c r="B170" s="2" t="n">
-        <v>13</v>
+        <v>6</v>
       </c>
       <c r="C170" s="2" t="s">
-        <v>162</v>
+        <v>57</v>
       </c>
       <c r="D170" s="2" t="s">
         <v>358</v>
@@ -7936,16 +7936,16 @@
         <v>359</v>
       </c>
       <c r="F170" s="2" t="s">
-        <v>51</v>
+        <v>47</v>
       </c>
       <c r="G170" s="2" t="s">
-        <v>52</v>
+        <v>48</v>
       </c>
       <c r="H170" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I170" s="2" t="n">
-        <v>90.99</v>
+        <v>90.58</v>
       </c>
       <c r="J170" s="2" t="s">
         <v>16</v>
@@ -7956,10 +7956,10 @@
         <v>2022</v>
       </c>
       <c r="B171" s="2" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C171" s="2" t="s">
-        <v>61</v>
+        <v>54</v>
       </c>
       <c r="D171" s="2" t="s">
         <v>360</v>
@@ -7968,16 +7968,16 @@
         <v>361</v>
       </c>
       <c r="F171" s="2" t="s">
-        <v>51</v>
+        <v>47</v>
       </c>
       <c r="G171" s="2" t="s">
-        <v>52</v>
+        <v>48</v>
       </c>
       <c r="H171" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I171" s="2" t="n">
-        <v>90.58</v>
+        <v>90.24</v>
       </c>
       <c r="J171" s="2" t="s">
         <v>16</v>
@@ -7988,10 +7988,10 @@
         <v>2022</v>
       </c>
       <c r="B172" s="2" t="n">
-        <v>5</v>
+        <v>13</v>
       </c>
       <c r="C172" s="2" t="s">
-        <v>58</v>
+        <v>160</v>
       </c>
       <c r="D172" s="2" t="s">
         <v>362</v>
@@ -8000,16 +8000,16 @@
         <v>363</v>
       </c>
       <c r="F172" s="2" t="s">
-        <v>51</v>
+        <v>47</v>
       </c>
       <c r="G172" s="2" t="s">
-        <v>52</v>
+        <v>48</v>
       </c>
       <c r="H172" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I172" s="2" t="n">
-        <v>90.24</v>
+        <v>90.19</v>
       </c>
       <c r="J172" s="2" t="s">
         <v>16</v>
@@ -8020,10 +8020,10 @@
         <v>2022</v>
       </c>
       <c r="B173" s="2" t="n">
-        <v>13</v>
+        <v>6</v>
       </c>
       <c r="C173" s="2" t="s">
-        <v>162</v>
+        <v>57</v>
       </c>
       <c r="D173" s="2" t="s">
         <v>364</v>
@@ -8032,16 +8032,16 @@
         <v>365</v>
       </c>
       <c r="F173" s="2" t="s">
-        <v>51</v>
+        <v>47</v>
       </c>
       <c r="G173" s="2" t="s">
-        <v>52</v>
+        <v>48</v>
       </c>
       <c r="H173" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I173" s="2" t="n">
-        <v>90.19</v>
+        <v>89.47</v>
       </c>
       <c r="J173" s="2" t="s">
         <v>16</v>
@@ -8052,10 +8052,10 @@
         <v>2022</v>
       </c>
       <c r="B174" s="2" t="n">
-        <v>6</v>
+        <v>13</v>
       </c>
       <c r="C174" s="2" t="s">
-        <v>61</v>
+        <v>160</v>
       </c>
       <c r="D174" s="2" t="s">
         <v>366</v>
@@ -8064,16 +8064,16 @@
         <v>367</v>
       </c>
       <c r="F174" s="2" t="s">
-        <v>51</v>
+        <v>47</v>
       </c>
       <c r="G174" s="2" t="s">
-        <v>52</v>
+        <v>48</v>
       </c>
       <c r="H174" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I174" s="2" t="n">
-        <v>89.47</v>
+        <v>89.41</v>
       </c>
       <c r="J174" s="2" t="s">
         <v>16</v>
@@ -8084,10 +8084,10 @@
         <v>2022</v>
       </c>
       <c r="B175" s="2" t="n">
-        <v>13</v>
+        <v>5</v>
       </c>
       <c r="C175" s="2" t="s">
-        <v>162</v>
+        <v>54</v>
       </c>
       <c r="D175" s="2" t="s">
         <v>368</v>
@@ -8096,16 +8096,16 @@
         <v>369</v>
       </c>
       <c r="F175" s="2" t="s">
-        <v>51</v>
+        <v>47</v>
       </c>
       <c r="G175" s="2" t="s">
-        <v>52</v>
+        <v>48</v>
       </c>
       <c r="H175" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I175" s="2" t="n">
-        <v>89.41</v>
+        <v>89.33</v>
       </c>
       <c r="J175" s="2" t="s">
         <v>16</v>
@@ -8119,7 +8119,7 @@
         <v>5</v>
       </c>
       <c r="C176" s="2" t="s">
-        <v>58</v>
+        <v>54</v>
       </c>
       <c r="D176" s="2" t="s">
         <v>370</v>
@@ -8128,16 +8128,16 @@
         <v>371</v>
       </c>
       <c r="F176" s="2" t="s">
-        <v>51</v>
+        <v>47</v>
       </c>
       <c r="G176" s="2" t="s">
-        <v>52</v>
+        <v>48</v>
       </c>
       <c r="H176" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I176" s="2" t="n">
-        <v>89.33</v>
+        <v>88.41</v>
       </c>
       <c r="J176" s="2" t="s">
         <v>16</v>
@@ -8151,7 +8151,7 @@
         <v>5</v>
       </c>
       <c r="C177" s="2" t="s">
-        <v>58</v>
+        <v>54</v>
       </c>
       <c r="D177" s="2" t="s">
         <v>372</v>
@@ -8160,16 +8160,16 @@
         <v>373</v>
       </c>
       <c r="F177" s="2" t="s">
-        <v>51</v>
+        <v>47</v>
       </c>
       <c r="G177" s="2" t="s">
-        <v>52</v>
+        <v>48</v>
       </c>
       <c r="H177" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I177" s="2" t="n">
-        <v>88.41</v>
+        <v>87.77</v>
       </c>
       <c r="J177" s="2" t="s">
         <v>16</v>
@@ -8180,10 +8180,10 @@
         <v>2022</v>
       </c>
       <c r="B178" s="2" t="n">
-        <v>5</v>
+        <v>13</v>
       </c>
       <c r="C178" s="2" t="s">
-        <v>58</v>
+        <v>160</v>
       </c>
       <c r="D178" s="2" t="s">
         <v>374</v>
@@ -8192,16 +8192,16 @@
         <v>375</v>
       </c>
       <c r="F178" s="2" t="s">
-        <v>51</v>
+        <v>47</v>
       </c>
       <c r="G178" s="2" t="s">
-        <v>52</v>
+        <v>48</v>
       </c>
       <c r="H178" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I178" s="2" t="n">
-        <v>87.77</v>
+        <v>87.52</v>
       </c>
       <c r="J178" s="2" t="s">
         <v>16</v>
@@ -8212,10 +8212,10 @@
         <v>2022</v>
       </c>
       <c r="B179" s="2" t="n">
-        <v>13</v>
+        <v>5</v>
       </c>
       <c r="C179" s="2" t="s">
-        <v>162</v>
+        <v>54</v>
       </c>
       <c r="D179" s="2" t="s">
         <v>376</v>
@@ -8224,16 +8224,16 @@
         <v>377</v>
       </c>
       <c r="F179" s="2" t="s">
-        <v>51</v>
+        <v>47</v>
       </c>
       <c r="G179" s="2" t="s">
-        <v>52</v>
+        <v>48</v>
       </c>
       <c r="H179" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I179" s="2" t="n">
-        <v>87.52</v>
+        <v>84.17</v>
       </c>
       <c r="J179" s="2" t="s">
         <v>16</v>
@@ -8244,10 +8244,10 @@
         <v>2022</v>
       </c>
       <c r="B180" s="2" t="n">
-        <v>5</v>
+        <v>13</v>
       </c>
       <c r="C180" s="2" t="s">
-        <v>58</v>
+        <v>160</v>
       </c>
       <c r="D180" s="2" t="s">
         <v>378</v>
@@ -8256,16 +8256,16 @@
         <v>379</v>
       </c>
       <c r="F180" s="2" t="s">
-        <v>51</v>
+        <v>47</v>
       </c>
       <c r="G180" s="2" t="s">
-        <v>52</v>
+        <v>48</v>
       </c>
       <c r="H180" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I180" s="2" t="n">
-        <v>84.17</v>
+        <v>83.92</v>
       </c>
       <c r="J180" s="2" t="s">
         <v>16</v>
@@ -8279,7 +8279,7 @@
         <v>13</v>
       </c>
       <c r="C181" s="2" t="s">
-        <v>162</v>
+        <v>160</v>
       </c>
       <c r="D181" s="2" t="s">
         <v>380</v>
@@ -8288,16 +8288,16 @@
         <v>381</v>
       </c>
       <c r="F181" s="2" t="s">
-        <v>51</v>
+        <v>47</v>
       </c>
       <c r="G181" s="2" t="s">
-        <v>52</v>
+        <v>48</v>
       </c>
       <c r="H181" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I181" s="2" t="n">
-        <v>83.92</v>
+        <v>82.13</v>
       </c>
       <c r="J181" s="2" t="s">
         <v>16</v>
@@ -8308,28 +8308,28 @@
         <v>2022</v>
       </c>
       <c r="B182" s="2" t="n">
-        <v>13</v>
+        <v>4</v>
       </c>
       <c r="C182" s="2" t="s">
-        <v>162</v>
+        <v>382</v>
       </c>
       <c r="D182" s="2" t="s">
-        <v>382</v>
+        <v>383</v>
       </c>
       <c r="E182" s="2" t="s">
-        <v>383</v>
+        <v>384</v>
       </c>
       <c r="F182" s="2" t="s">
-        <v>51</v>
+        <v>385</v>
       </c>
       <c r="G182" s="2" t="s">
-        <v>52</v>
+        <v>386</v>
       </c>
       <c r="H182" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I182" s="2" t="n">
-        <v>82.13</v>
+        <v>98.91</v>
       </c>
       <c r="J182" s="2" t="s">
         <v>16</v>
@@ -8343,25 +8343,25 @@
         <v>4</v>
       </c>
       <c r="C183" s="2" t="s">
-        <v>384</v>
+        <v>382</v>
       </c>
       <c r="D183" s="2" t="s">
+        <v>387</v>
+      </c>
+      <c r="E183" s="2" t="s">
+        <v>388</v>
+      </c>
+      <c r="F183" s="2" t="s">
         <v>385</v>
       </c>
-      <c r="E183" s="2" t="s">
+      <c r="G183" s="2" t="s">
         <v>386</v>
       </c>
-      <c r="F183" s="2" t="s">
-        <v>387</v>
-      </c>
-      <c r="G183" s="2" t="s">
-        <v>388</v>
-      </c>
       <c r="H183" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I183" s="2" t="n">
-        <v>98.91</v>
+        <v>97.76</v>
       </c>
       <c r="J183" s="2" t="s">
         <v>16</v>
@@ -8372,28 +8372,28 @@
         <v>2022</v>
       </c>
       <c r="B184" s="2" t="n">
-        <v>4</v>
+        <v>15</v>
       </c>
       <c r="C184" s="2" t="s">
-        <v>384</v>
+        <v>389</v>
       </c>
       <c r="D184" s="2" t="s">
-        <v>389</v>
+        <v>390</v>
       </c>
       <c r="E184" s="2" t="s">
-        <v>390</v>
+        <v>391</v>
       </c>
       <c r="F184" s="2" t="s">
-        <v>387</v>
+        <v>385</v>
       </c>
       <c r="G184" s="2" t="s">
-        <v>388</v>
+        <v>386</v>
       </c>
       <c r="H184" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I184" s="2" t="n">
-        <v>97.76</v>
+        <v>97.48</v>
       </c>
       <c r="J184" s="2" t="s">
         <v>16</v>
@@ -8404,10 +8404,10 @@
         <v>2022</v>
       </c>
       <c r="B185" s="2" t="n">
-        <v>15</v>
+        <v>4</v>
       </c>
       <c r="C185" s="2" t="s">
-        <v>391</v>
+        <v>382</v>
       </c>
       <c r="D185" s="2" t="s">
         <v>392</v>
@@ -8416,16 +8416,16 @@
         <v>393</v>
       </c>
       <c r="F185" s="2" t="s">
-        <v>387</v>
+        <v>385</v>
       </c>
       <c r="G185" s="2" t="s">
-        <v>388</v>
+        <v>386</v>
       </c>
       <c r="H185" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I185" s="2" t="n">
-        <v>97.48</v>
+        <v>97.37</v>
       </c>
       <c r="J185" s="2" t="s">
         <v>16</v>
@@ -8439,7 +8439,7 @@
         <v>4</v>
       </c>
       <c r="C186" s="2" t="s">
-        <v>384</v>
+        <v>382</v>
       </c>
       <c r="D186" s="2" t="s">
         <v>394</v>
@@ -8448,16 +8448,16 @@
         <v>395</v>
       </c>
       <c r="F186" s="2" t="s">
-        <v>387</v>
+        <v>385</v>
       </c>
       <c r="G186" s="2" t="s">
-        <v>388</v>
+        <v>386</v>
       </c>
       <c r="H186" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I186" s="2" t="n">
-        <v>97.37</v>
+        <v>97.33</v>
       </c>
       <c r="J186" s="2" t="s">
         <v>16</v>
@@ -8471,7 +8471,7 @@
         <v>4</v>
       </c>
       <c r="C187" s="2" t="s">
-        <v>384</v>
+        <v>382</v>
       </c>
       <c r="D187" s="2" t="s">
         <v>396</v>
@@ -8480,16 +8480,16 @@
         <v>397</v>
       </c>
       <c r="F187" s="2" t="s">
-        <v>387</v>
+        <v>385</v>
       </c>
       <c r="G187" s="2" t="s">
-        <v>388</v>
+        <v>386</v>
       </c>
       <c r="H187" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I187" s="2" t="n">
-        <v>97.33</v>
+        <v>97.24</v>
       </c>
       <c r="J187" s="2" t="s">
         <v>16</v>
@@ -8503,7 +8503,7 @@
         <v>4</v>
       </c>
       <c r="C188" s="2" t="s">
-        <v>384</v>
+        <v>382</v>
       </c>
       <c r="D188" s="2" t="s">
         <v>398</v>
@@ -8512,16 +8512,16 @@
         <v>399</v>
       </c>
       <c r="F188" s="2" t="s">
-        <v>387</v>
+        <v>385</v>
       </c>
       <c r="G188" s="2" t="s">
-        <v>388</v>
+        <v>386</v>
       </c>
       <c r="H188" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I188" s="2" t="n">
-        <v>97.24</v>
+        <v>96.9</v>
       </c>
       <c r="J188" s="2" t="s">
         <v>16</v>
@@ -8535,7 +8535,7 @@
         <v>4</v>
       </c>
       <c r="C189" s="2" t="s">
-        <v>384</v>
+        <v>382</v>
       </c>
       <c r="D189" s="2" t="s">
         <v>400</v>
@@ -8544,16 +8544,16 @@
         <v>401</v>
       </c>
       <c r="F189" s="2" t="s">
-        <v>387</v>
+        <v>385</v>
       </c>
       <c r="G189" s="2" t="s">
-        <v>388</v>
+        <v>386</v>
       </c>
       <c r="H189" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I189" s="2" t="n">
-        <v>96.9</v>
+        <v>96.58</v>
       </c>
       <c r="J189" s="2" t="s">
         <v>16</v>
@@ -8564,28 +8564,28 @@
         <v>2022</v>
       </c>
       <c r="B190" s="2" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C190" s="2" t="s">
-        <v>384</v>
+        <v>402</v>
       </c>
       <c r="D190" s="2" t="s">
-        <v>402</v>
+        <v>403</v>
       </c>
       <c r="E190" s="2" t="s">
-        <v>403</v>
+        <v>404</v>
       </c>
       <c r="F190" s="2" t="s">
-        <v>387</v>
+        <v>385</v>
       </c>
       <c r="G190" s="2" t="s">
-        <v>388</v>
+        <v>386</v>
       </c>
       <c r="H190" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I190" s="2" t="n">
-        <v>96.58</v>
+        <v>96.42</v>
       </c>
       <c r="J190" s="2" t="s">
         <v>16</v>
@@ -8599,7 +8599,7 @@
         <v>3</v>
       </c>
       <c r="C191" s="2" t="s">
-        <v>404</v>
+        <v>402</v>
       </c>
       <c r="D191" s="2" t="s">
         <v>405</v>
@@ -8608,10 +8608,10 @@
         <v>406</v>
       </c>
       <c r="F191" s="2" t="s">
-        <v>387</v>
+        <v>385</v>
       </c>
       <c r="G191" s="2" t="s">
-        <v>388</v>
+        <v>386</v>
       </c>
       <c r="H191" s="2" t="s">
         <v>15</v>
@@ -8628,10 +8628,10 @@
         <v>2022</v>
       </c>
       <c r="B192" s="2" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C192" s="2" t="s">
-        <v>404</v>
+        <v>382</v>
       </c>
       <c r="D192" s="2" t="s">
         <v>407</v>
@@ -8640,16 +8640,16 @@
         <v>408</v>
       </c>
       <c r="F192" s="2" t="s">
-        <v>387</v>
+        <v>385</v>
       </c>
       <c r="G192" s="2" t="s">
-        <v>388</v>
+        <v>386</v>
       </c>
       <c r="H192" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I192" s="2" t="n">
-        <v>96.42</v>
+        <v>96.37</v>
       </c>
       <c r="J192" s="2" t="s">
         <v>16</v>
@@ -8663,7 +8663,7 @@
         <v>4</v>
       </c>
       <c r="C193" s="2" t="s">
-        <v>384</v>
+        <v>382</v>
       </c>
       <c r="D193" s="2" t="s">
         <v>409</v>
@@ -8672,16 +8672,16 @@
         <v>410</v>
       </c>
       <c r="F193" s="2" t="s">
-        <v>387</v>
+        <v>385</v>
       </c>
       <c r="G193" s="2" t="s">
-        <v>388</v>
+        <v>386</v>
       </c>
       <c r="H193" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I193" s="2" t="n">
-        <v>96.37</v>
+        <v>96.28</v>
       </c>
       <c r="J193" s="2" t="s">
         <v>16</v>
@@ -8692,10 +8692,10 @@
         <v>2022</v>
       </c>
       <c r="B194" s="2" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C194" s="2" t="s">
-        <v>384</v>
+        <v>402</v>
       </c>
       <c r="D194" s="2" t="s">
         <v>411</v>
@@ -8704,16 +8704,16 @@
         <v>412</v>
       </c>
       <c r="F194" s="2" t="s">
-        <v>387</v>
+        <v>385</v>
       </c>
       <c r="G194" s="2" t="s">
-        <v>388</v>
+        <v>386</v>
       </c>
       <c r="H194" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I194" s="2" t="n">
-        <v>96.28</v>
+        <v>96.27</v>
       </c>
       <c r="J194" s="2" t="s">
         <v>16</v>
@@ -8727,7 +8727,7 @@
         <v>3</v>
       </c>
       <c r="C195" s="2" t="s">
-        <v>404</v>
+        <v>402</v>
       </c>
       <c r="D195" s="2" t="s">
         <v>413</v>
@@ -8736,16 +8736,16 @@
         <v>414</v>
       </c>
       <c r="F195" s="2" t="s">
-        <v>387</v>
+        <v>385</v>
       </c>
       <c r="G195" s="2" t="s">
-        <v>388</v>
+        <v>386</v>
       </c>
       <c r="H195" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I195" s="2" t="n">
-        <v>96.27</v>
+        <v>96.15</v>
       </c>
       <c r="J195" s="2" t="s">
         <v>16</v>
@@ -8756,10 +8756,10 @@
         <v>2022</v>
       </c>
       <c r="B196" s="2" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C196" s="2" t="s">
-        <v>404</v>
+        <v>382</v>
       </c>
       <c r="D196" s="2" t="s">
         <v>415</v>
@@ -8768,10 +8768,10 @@
         <v>416</v>
       </c>
       <c r="F196" s="2" t="s">
-        <v>387</v>
+        <v>385</v>
       </c>
       <c r="G196" s="2" t="s">
-        <v>388</v>
+        <v>386</v>
       </c>
       <c r="H196" s="2" t="s">
         <v>15</v>
@@ -8791,7 +8791,7 @@
         <v>4</v>
       </c>
       <c r="C197" s="2" t="s">
-        <v>384</v>
+        <v>382</v>
       </c>
       <c r="D197" s="2" t="s">
         <v>417</v>
@@ -8800,16 +8800,16 @@
         <v>418</v>
       </c>
       <c r="F197" s="2" t="s">
-        <v>387</v>
+        <v>385</v>
       </c>
       <c r="G197" s="2" t="s">
-        <v>388</v>
+        <v>386</v>
       </c>
       <c r="H197" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I197" s="2" t="n">
-        <v>96.15</v>
+        <v>95.72</v>
       </c>
       <c r="J197" s="2" t="s">
         <v>16</v>
@@ -8823,7 +8823,7 @@
         <v>4</v>
       </c>
       <c r="C198" s="2" t="s">
-        <v>384</v>
+        <v>382</v>
       </c>
       <c r="D198" s="2" t="s">
         <v>419</v>
@@ -8832,16 +8832,16 @@
         <v>420</v>
       </c>
       <c r="F198" s="2" t="s">
-        <v>387</v>
+        <v>385</v>
       </c>
       <c r="G198" s="2" t="s">
-        <v>388</v>
+        <v>386</v>
       </c>
       <c r="H198" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I198" s="2" t="n">
-        <v>95.72</v>
+        <v>95.67</v>
       </c>
       <c r="J198" s="2" t="s">
         <v>16</v>
@@ -8852,10 +8852,10 @@
         <v>2022</v>
       </c>
       <c r="B199" s="2" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C199" s="2" t="s">
-        <v>384</v>
+        <v>402</v>
       </c>
       <c r="D199" s="2" t="s">
         <v>421</v>
@@ -8864,16 +8864,16 @@
         <v>422</v>
       </c>
       <c r="F199" s="2" t="s">
-        <v>387</v>
+        <v>385</v>
       </c>
       <c r="G199" s="2" t="s">
-        <v>388</v>
+        <v>386</v>
       </c>
       <c r="H199" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I199" s="2" t="n">
-        <v>95.67</v>
+        <v>95.64</v>
       </c>
       <c r="J199" s="2" t="s">
         <v>16</v>
@@ -8884,10 +8884,10 @@
         <v>2022</v>
       </c>
       <c r="B200" s="2" t="n">
-        <v>3</v>
+        <v>15</v>
       </c>
       <c r="C200" s="2" t="s">
-        <v>404</v>
+        <v>389</v>
       </c>
       <c r="D200" s="2" t="s">
         <v>423</v>
@@ -8896,16 +8896,16 @@
         <v>424</v>
       </c>
       <c r="F200" s="2" t="s">
-        <v>387</v>
+        <v>385</v>
       </c>
       <c r="G200" s="2" t="s">
-        <v>388</v>
+        <v>386</v>
       </c>
       <c r="H200" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I200" s="2" t="n">
-        <v>95.64</v>
+        <v>95.56</v>
       </c>
       <c r="J200" s="2" t="s">
         <v>16</v>
@@ -8916,28 +8916,28 @@
         <v>2022</v>
       </c>
       <c r="B201" s="2" t="n">
-        <v>15</v>
+        <v>1</v>
       </c>
       <c r="C201" s="2" t="s">
-        <v>391</v>
+        <v>425</v>
       </c>
       <c r="D201" s="2" t="s">
-        <v>425</v>
+        <v>426</v>
       </c>
       <c r="E201" s="2" t="s">
-        <v>426</v>
+        <v>427</v>
       </c>
       <c r="F201" s="2" t="s">
-        <v>387</v>
+        <v>385</v>
       </c>
       <c r="G201" s="2" t="s">
-        <v>388</v>
+        <v>386</v>
       </c>
       <c r="H201" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I201" s="2" t="n">
-        <v>95.56</v>
+        <v>95.45</v>
       </c>
       <c r="J201" s="2" t="s">
         <v>16</v>
@@ -8948,10 +8948,10 @@
         <v>2022</v>
       </c>
       <c r="B202" s="2" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C202" s="2" t="s">
-        <v>427</v>
+        <v>402</v>
       </c>
       <c r="D202" s="2" t="s">
         <v>428</v>
@@ -8960,16 +8960,16 @@
         <v>429</v>
       </c>
       <c r="F202" s="2" t="s">
-        <v>387</v>
+        <v>385</v>
       </c>
       <c r="G202" s="2" t="s">
-        <v>388</v>
+        <v>386</v>
       </c>
       <c r="H202" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I202" s="2" t="n">
-        <v>95.45</v>
+        <v>95.41</v>
       </c>
       <c r="J202" s="2" t="s">
         <v>16</v>
@@ -8980,28 +8980,28 @@
         <v>2022</v>
       </c>
       <c r="B203" s="2" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C203" s="2" t="s">
-        <v>404</v>
+        <v>430</v>
       </c>
       <c r="D203" s="2" t="s">
-        <v>430</v>
+        <v>431</v>
       </c>
       <c r="E203" s="2" t="s">
-        <v>431</v>
+        <v>432</v>
       </c>
       <c r="F203" s="2" t="s">
-        <v>387</v>
+        <v>385</v>
       </c>
       <c r="G203" s="2" t="s">
-        <v>388</v>
+        <v>386</v>
       </c>
       <c r="H203" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I203" s="2" t="n">
-        <v>95.41</v>
+        <v>95.26</v>
       </c>
       <c r="J203" s="2" t="s">
         <v>16</v>
@@ -9012,10 +9012,10 @@
         <v>2022</v>
       </c>
       <c r="B204" s="2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C204" s="2" t="s">
-        <v>432</v>
+        <v>402</v>
       </c>
       <c r="D204" s="2" t="s">
         <v>433</v>
@@ -9024,16 +9024,16 @@
         <v>434</v>
       </c>
       <c r="F204" s="2" t="s">
-        <v>387</v>
+        <v>385</v>
       </c>
       <c r="G204" s="2" t="s">
-        <v>388</v>
+        <v>386</v>
       </c>
       <c r="H204" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I204" s="2" t="n">
-        <v>95.26</v>
+        <v>95.18</v>
       </c>
       <c r="J204" s="2" t="s">
         <v>16</v>
@@ -9044,10 +9044,10 @@
         <v>2022</v>
       </c>
       <c r="B205" s="2" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C205" s="2" t="s">
-        <v>404</v>
+        <v>382</v>
       </c>
       <c r="D205" s="2" t="s">
         <v>435</v>
@@ -9056,16 +9056,16 @@
         <v>436</v>
       </c>
       <c r="F205" s="2" t="s">
-        <v>387</v>
+        <v>385</v>
       </c>
       <c r="G205" s="2" t="s">
-        <v>388</v>
+        <v>386</v>
       </c>
       <c r="H205" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I205" s="2" t="n">
-        <v>95.18</v>
+        <v>95.06</v>
       </c>
       <c r="J205" s="2" t="s">
         <v>16</v>
@@ -9079,7 +9079,7 @@
         <v>2</v>
       </c>
       <c r="C206" s="2" t="s">
-        <v>432</v>
+        <v>430</v>
       </c>
       <c r="D206" s="2" t="s">
         <v>437</v>
@@ -9088,10 +9088,10 @@
         <v>438</v>
       </c>
       <c r="F206" s="2" t="s">
-        <v>387</v>
+        <v>385</v>
       </c>
       <c r="G206" s="2" t="s">
-        <v>388</v>
+        <v>386</v>
       </c>
       <c r="H206" s="2" t="s">
         <v>15</v>
@@ -9111,7 +9111,7 @@
         <v>2</v>
       </c>
       <c r="C207" s="2" t="s">
-        <v>432</v>
+        <v>430</v>
       </c>
       <c r="D207" s="2" t="s">
         <v>439</v>
@@ -9120,10 +9120,10 @@
         <v>440</v>
       </c>
       <c r="F207" s="2" t="s">
-        <v>387</v>
+        <v>385</v>
       </c>
       <c r="G207" s="2" t="s">
-        <v>388</v>
+        <v>386</v>
       </c>
       <c r="H207" s="2" t="s">
         <v>15</v>
@@ -9143,19 +9143,19 @@
         <v>4</v>
       </c>
       <c r="C208" s="2" t="s">
-        <v>384</v>
+        <v>382</v>
       </c>
       <c r="D208" s="2" t="s">
         <v>441</v>
       </c>
       <c r="E208" s="2" t="s">
-        <v>384</v>
+        <v>382</v>
       </c>
       <c r="F208" s="2" t="s">
-        <v>387</v>
+        <v>385</v>
       </c>
       <c r="G208" s="2" t="s">
-        <v>388</v>
+        <v>386</v>
       </c>
       <c r="H208" s="2" t="s">
         <v>15</v>
@@ -9175,7 +9175,7 @@
         <v>3</v>
       </c>
       <c r="C209" s="2" t="s">
-        <v>404</v>
+        <v>402</v>
       </c>
       <c r="D209" s="2" t="s">
         <v>442</v>
@@ -9184,10 +9184,10 @@
         <v>443</v>
       </c>
       <c r="F209" s="2" t="s">
-        <v>387</v>
+        <v>385</v>
       </c>
       <c r="G209" s="2" t="s">
-        <v>388</v>
+        <v>386</v>
       </c>
       <c r="H209" s="2" t="s">
         <v>15</v>
@@ -9207,7 +9207,7 @@
         <v>3</v>
       </c>
       <c r="C210" s="2" t="s">
-        <v>404</v>
+        <v>402</v>
       </c>
       <c r="D210" s="2" t="s">
         <v>444</v>
@@ -9216,10 +9216,10 @@
         <v>445</v>
       </c>
       <c r="F210" s="2" t="s">
-        <v>387</v>
+        <v>385</v>
       </c>
       <c r="G210" s="2" t="s">
-        <v>388</v>
+        <v>386</v>
       </c>
       <c r="H210" s="2" t="s">
         <v>15</v>
@@ -9239,7 +9239,7 @@
         <v>1</v>
       </c>
       <c r="C211" s="2" t="s">
-        <v>427</v>
+        <v>425</v>
       </c>
       <c r="D211" s="2" t="s">
         <v>446</v>
@@ -9248,10 +9248,10 @@
         <v>447</v>
       </c>
       <c r="F211" s="2" t="s">
-        <v>387</v>
+        <v>385</v>
       </c>
       <c r="G211" s="2" t="s">
-        <v>388</v>
+        <v>386</v>
       </c>
       <c r="H211" s="2" t="s">
         <v>15</v>
@@ -9271,7 +9271,7 @@
         <v>4</v>
       </c>
       <c r="C212" s="2" t="s">
-        <v>384</v>
+        <v>382</v>
       </c>
       <c r="D212" s="2" t="s">
         <v>448</v>
@@ -9280,10 +9280,10 @@
         <v>449</v>
       </c>
       <c r="F212" s="2" t="s">
-        <v>387</v>
+        <v>385</v>
       </c>
       <c r="G212" s="2" t="s">
-        <v>388</v>
+        <v>386</v>
       </c>
       <c r="H212" s="2" t="s">
         <v>15</v>
@@ -9303,7 +9303,7 @@
         <v>2</v>
       </c>
       <c r="C213" s="2" t="s">
-        <v>432</v>
+        <v>430</v>
       </c>
       <c r="D213" s="2" t="s">
         <v>450</v>
@@ -9312,10 +9312,10 @@
         <v>451</v>
       </c>
       <c r="F213" s="2" t="s">
-        <v>387</v>
+        <v>385</v>
       </c>
       <c r="G213" s="2" t="s">
-        <v>388</v>
+        <v>386</v>
       </c>
       <c r="H213" s="2" t="s">
         <v>15</v>
@@ -9335,7 +9335,7 @@
         <v>1</v>
       </c>
       <c r="C214" s="2" t="s">
-        <v>427</v>
+        <v>425</v>
       </c>
       <c r="D214" s="2" t="s">
         <v>452</v>
@@ -9344,10 +9344,10 @@
         <v>453</v>
       </c>
       <c r="F214" s="2" t="s">
-        <v>387</v>
+        <v>385</v>
       </c>
       <c r="G214" s="2" t="s">
-        <v>388</v>
+        <v>386</v>
       </c>
       <c r="H214" s="2" t="s">
         <v>15</v>
@@ -9367,7 +9367,7 @@
         <v>15</v>
       </c>
       <c r="C215" s="2" t="s">
-        <v>391</v>
+        <v>389</v>
       </c>
       <c r="D215" s="2" t="s">
         <v>454</v>
@@ -9376,10 +9376,10 @@
         <v>455</v>
       </c>
       <c r="F215" s="2" t="s">
-        <v>387</v>
+        <v>385</v>
       </c>
       <c r="G215" s="2" t="s">
-        <v>388</v>
+        <v>386</v>
       </c>
       <c r="H215" s="2" t="s">
         <v>15</v>
@@ -9399,7 +9399,7 @@
         <v>1</v>
       </c>
       <c r="C216" s="2" t="s">
-        <v>427</v>
+        <v>425</v>
       </c>
       <c r="D216" s="2" t="s">
         <v>456</v>
@@ -9408,10 +9408,10 @@
         <v>457</v>
       </c>
       <c r="F216" s="2" t="s">
-        <v>387</v>
+        <v>385</v>
       </c>
       <c r="G216" s="2" t="s">
-        <v>388</v>
+        <v>386</v>
       </c>
       <c r="H216" s="2" t="s">
         <v>15</v>
@@ -9431,7 +9431,7 @@
         <v>2</v>
       </c>
       <c r="C217" s="2" t="s">
-        <v>432</v>
+        <v>430</v>
       </c>
       <c r="D217" s="2" t="s">
         <v>458</v>
@@ -9440,10 +9440,10 @@
         <v>459</v>
       </c>
       <c r="F217" s="2" t="s">
-        <v>387</v>
+        <v>385</v>
       </c>
       <c r="G217" s="2" t="s">
-        <v>388</v>
+        <v>386</v>
       </c>
       <c r="H217" s="2" t="s">
         <v>15</v>
@@ -9463,7 +9463,7 @@
         <v>1</v>
       </c>
       <c r="C218" s="2" t="s">
-        <v>427</v>
+        <v>425</v>
       </c>
       <c r="D218" s="2" t="s">
         <v>460</v>
@@ -9472,10 +9472,10 @@
         <v>461</v>
       </c>
       <c r="F218" s="2" t="s">
-        <v>387</v>
+        <v>385</v>
       </c>
       <c r="G218" s="2" t="s">
-        <v>388</v>
+        <v>386</v>
       </c>
       <c r="H218" s="2" t="s">
         <v>15</v>
@@ -9495,7 +9495,7 @@
         <v>1</v>
       </c>
       <c r="C219" s="2" t="s">
-        <v>427</v>
+        <v>425</v>
       </c>
       <c r="D219" s="2" t="s">
         <v>462</v>
@@ -9504,10 +9504,10 @@
         <v>463</v>
       </c>
       <c r="F219" s="2" t="s">
-        <v>387</v>
+        <v>385</v>
       </c>
       <c r="G219" s="2" t="s">
-        <v>388</v>
+        <v>386</v>
       </c>
       <c r="H219" s="2" t="s">
         <v>15</v>
@@ -9527,19 +9527,19 @@
         <v>2</v>
       </c>
       <c r="C220" s="2" t="s">
-        <v>432</v>
+        <v>430</v>
       </c>
       <c r="D220" s="2" t="s">
         <v>464</v>
       </c>
       <c r="E220" s="2" t="s">
-        <v>432</v>
+        <v>430</v>
       </c>
       <c r="F220" s="2" t="s">
-        <v>387</v>
+        <v>385</v>
       </c>
       <c r="G220" s="2" t="s">
-        <v>388</v>
+        <v>386</v>
       </c>
       <c r="H220" s="2" t="s">
         <v>15</v>
@@ -9559,7 +9559,7 @@
         <v>2</v>
       </c>
       <c r="C221" s="2" t="s">
-        <v>432</v>
+        <v>430</v>
       </c>
       <c r="D221" s="2" t="s">
         <v>465</v>
@@ -9568,10 +9568,10 @@
         <v>466</v>
       </c>
       <c r="F221" s="2" t="s">
-        <v>387</v>
+        <v>385</v>
       </c>
       <c r="G221" s="2" t="s">
-        <v>388</v>
+        <v>386</v>
       </c>
       <c r="H221" s="2" t="s">
         <v>15</v>
@@ -9591,7 +9591,7 @@
         <v>2</v>
       </c>
       <c r="C222" s="2" t="s">
-        <v>432</v>
+        <v>430</v>
       </c>
       <c r="D222" s="2" t="s">
         <v>467</v>
@@ -9600,10 +9600,10 @@
         <v>468</v>
       </c>
       <c r="F222" s="2" t="s">
-        <v>387</v>
+        <v>385</v>
       </c>
       <c r="G222" s="2" t="s">
-        <v>388</v>
+        <v>386</v>
       </c>
       <c r="H222" s="2" t="s">
         <v>15</v>
@@ -9623,7 +9623,7 @@
         <v>1</v>
       </c>
       <c r="C223" s="2" t="s">
-        <v>427</v>
+        <v>425</v>
       </c>
       <c r="D223" s="2" t="s">
         <v>469</v>
@@ -9632,10 +9632,10 @@
         <v>470</v>
       </c>
       <c r="F223" s="2" t="s">
-        <v>387</v>
+        <v>385</v>
       </c>
       <c r="G223" s="2" t="s">
-        <v>388</v>
+        <v>386</v>
       </c>
       <c r="H223" s="2" t="s">
         <v>15</v>

--- a/output/graficos_nacionales/plot_nacional_e_basneta_a_2022.xlsx
+++ b/output/graficos_nacionales/plot_nacional_e_basneta_a_2022.xlsx
@@ -2089,7 +2089,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-09 20:12</t>
+    <t xml:space="preserve">2026-09-18 11:32</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_nacionales/plot_nacional_e_basneta_a_2022.xlsx
+++ b/output/graficos_nacionales/plot_nacional_e_basneta_a_2022.xlsx
@@ -2089,7 +2089,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-18 11:32</t>
+    <t xml:space="preserve">2026-09-24 00:24</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>
